--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SUKCO0665\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB78EFF-72CF-4161-A7E9-7B6EEDE8C681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB2C0C8-74D8-4257-B448-833025637023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{4E7050FE-42BA-4739-8710-2FFE42CC73BF}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" activeTab="3" xr2:uid="{4E7050FE-42BA-4739-8710-2FFE42CC73BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="541">
   <si>
     <t>Sridhar Durve</t>
   </si>
@@ -1653,6 +1653,15 @@
   </si>
   <si>
     <t>Madhav Sridhar_Durve</t>
+  </si>
+  <si>
+    <t>Kavyansh</t>
+  </si>
+  <si>
+    <t>https://github.com/nakuldurve-web/family-tree-web</t>
+  </si>
+  <si>
+    <t>https://github.com/sbdurve/family-tree-web</t>
   </si>
 </sst>
 </file>
@@ -2047,648 +2056,648 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{638F9C91-F3D4-4735-B7D1-3C3820A30CDB}">
   <dimension ref="A1:H119"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="34.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" customWidth="1"/>
-    <col min="7" max="7" width="8.42578125" customWidth="1"/>
-    <col min="252" max="252" width="7.28515625" customWidth="1"/>
-    <col min="253" max="253" width="19.42578125" customWidth="1"/>
-    <col min="254" max="254" width="2.85546875" customWidth="1"/>
-    <col min="255" max="255" width="5.5703125" customWidth="1"/>
-    <col min="256" max="256" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="257" max="257" width="23.28515625" customWidth="1"/>
-    <col min="258" max="258" width="10.28515625" customWidth="1"/>
-    <col min="259" max="259" width="19.42578125" customWidth="1"/>
-    <col min="260" max="260" width="9.28515625" customWidth="1"/>
-    <col min="261" max="262" width="19.42578125" customWidth="1"/>
-    <col min="508" max="508" width="7.28515625" customWidth="1"/>
-    <col min="509" max="509" width="19.42578125" customWidth="1"/>
-    <col min="510" max="510" width="2.85546875" customWidth="1"/>
-    <col min="511" max="511" width="5.5703125" customWidth="1"/>
-    <col min="512" max="512" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="513" max="513" width="23.28515625" customWidth="1"/>
-    <col min="514" max="514" width="10.28515625" customWidth="1"/>
-    <col min="515" max="515" width="19.42578125" customWidth="1"/>
-    <col min="516" max="516" width="9.28515625" customWidth="1"/>
-    <col min="517" max="518" width="19.42578125" customWidth="1"/>
-    <col min="764" max="764" width="7.28515625" customWidth="1"/>
-    <col min="765" max="765" width="19.42578125" customWidth="1"/>
-    <col min="766" max="766" width="2.85546875" customWidth="1"/>
-    <col min="767" max="767" width="5.5703125" customWidth="1"/>
-    <col min="768" max="768" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="769" max="769" width="23.28515625" customWidth="1"/>
-    <col min="770" max="770" width="10.28515625" customWidth="1"/>
-    <col min="771" max="771" width="19.42578125" customWidth="1"/>
-    <col min="772" max="772" width="9.28515625" customWidth="1"/>
-    <col min="773" max="774" width="19.42578125" customWidth="1"/>
-    <col min="1020" max="1020" width="7.28515625" customWidth="1"/>
-    <col min="1021" max="1021" width="19.42578125" customWidth="1"/>
-    <col min="1022" max="1022" width="2.85546875" customWidth="1"/>
-    <col min="1023" max="1023" width="5.5703125" customWidth="1"/>
-    <col min="1024" max="1024" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="1025" max="1025" width="23.28515625" customWidth="1"/>
-    <col min="1026" max="1026" width="10.28515625" customWidth="1"/>
-    <col min="1027" max="1027" width="19.42578125" customWidth="1"/>
-    <col min="1028" max="1028" width="9.28515625" customWidth="1"/>
-    <col min="1029" max="1030" width="19.42578125" customWidth="1"/>
-    <col min="1276" max="1276" width="7.28515625" customWidth="1"/>
-    <col min="1277" max="1277" width="19.42578125" customWidth="1"/>
-    <col min="1278" max="1278" width="2.85546875" customWidth="1"/>
-    <col min="1279" max="1279" width="5.5703125" customWidth="1"/>
-    <col min="1280" max="1280" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="1281" max="1281" width="23.28515625" customWidth="1"/>
-    <col min="1282" max="1282" width="10.28515625" customWidth="1"/>
-    <col min="1283" max="1283" width="19.42578125" customWidth="1"/>
-    <col min="1284" max="1284" width="9.28515625" customWidth="1"/>
-    <col min="1285" max="1286" width="19.42578125" customWidth="1"/>
-    <col min="1532" max="1532" width="7.28515625" customWidth="1"/>
-    <col min="1533" max="1533" width="19.42578125" customWidth="1"/>
-    <col min="1534" max="1534" width="2.85546875" customWidth="1"/>
-    <col min="1535" max="1535" width="5.5703125" customWidth="1"/>
-    <col min="1536" max="1536" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="1537" max="1537" width="23.28515625" customWidth="1"/>
-    <col min="1538" max="1538" width="10.28515625" customWidth="1"/>
-    <col min="1539" max="1539" width="19.42578125" customWidth="1"/>
-    <col min="1540" max="1540" width="9.28515625" customWidth="1"/>
-    <col min="1541" max="1542" width="19.42578125" customWidth="1"/>
-    <col min="1788" max="1788" width="7.28515625" customWidth="1"/>
-    <col min="1789" max="1789" width="19.42578125" customWidth="1"/>
-    <col min="1790" max="1790" width="2.85546875" customWidth="1"/>
-    <col min="1791" max="1791" width="5.5703125" customWidth="1"/>
-    <col min="1792" max="1792" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="1793" max="1793" width="23.28515625" customWidth="1"/>
-    <col min="1794" max="1794" width="10.28515625" customWidth="1"/>
-    <col min="1795" max="1795" width="19.42578125" customWidth="1"/>
-    <col min="1796" max="1796" width="9.28515625" customWidth="1"/>
-    <col min="1797" max="1798" width="19.42578125" customWidth="1"/>
-    <col min="2044" max="2044" width="7.28515625" customWidth="1"/>
-    <col min="2045" max="2045" width="19.42578125" customWidth="1"/>
-    <col min="2046" max="2046" width="2.85546875" customWidth="1"/>
-    <col min="2047" max="2047" width="5.5703125" customWidth="1"/>
-    <col min="2048" max="2048" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="2049" max="2049" width="23.28515625" customWidth="1"/>
-    <col min="2050" max="2050" width="10.28515625" customWidth="1"/>
-    <col min="2051" max="2051" width="19.42578125" customWidth="1"/>
-    <col min="2052" max="2052" width="9.28515625" customWidth="1"/>
-    <col min="2053" max="2054" width="19.42578125" customWidth="1"/>
-    <col min="2300" max="2300" width="7.28515625" customWidth="1"/>
-    <col min="2301" max="2301" width="19.42578125" customWidth="1"/>
-    <col min="2302" max="2302" width="2.85546875" customWidth="1"/>
-    <col min="2303" max="2303" width="5.5703125" customWidth="1"/>
-    <col min="2304" max="2304" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="2305" max="2305" width="23.28515625" customWidth="1"/>
-    <col min="2306" max="2306" width="10.28515625" customWidth="1"/>
-    <col min="2307" max="2307" width="19.42578125" customWidth="1"/>
-    <col min="2308" max="2308" width="9.28515625" customWidth="1"/>
-    <col min="2309" max="2310" width="19.42578125" customWidth="1"/>
-    <col min="2556" max="2556" width="7.28515625" customWidth="1"/>
-    <col min="2557" max="2557" width="19.42578125" customWidth="1"/>
-    <col min="2558" max="2558" width="2.85546875" customWidth="1"/>
-    <col min="2559" max="2559" width="5.5703125" customWidth="1"/>
-    <col min="2560" max="2560" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="2561" max="2561" width="23.28515625" customWidth="1"/>
-    <col min="2562" max="2562" width="10.28515625" customWidth="1"/>
-    <col min="2563" max="2563" width="19.42578125" customWidth="1"/>
-    <col min="2564" max="2564" width="9.28515625" customWidth="1"/>
-    <col min="2565" max="2566" width="19.42578125" customWidth="1"/>
-    <col min="2812" max="2812" width="7.28515625" customWidth="1"/>
-    <col min="2813" max="2813" width="19.42578125" customWidth="1"/>
-    <col min="2814" max="2814" width="2.85546875" customWidth="1"/>
-    <col min="2815" max="2815" width="5.5703125" customWidth="1"/>
-    <col min="2816" max="2816" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="2817" max="2817" width="23.28515625" customWidth="1"/>
-    <col min="2818" max="2818" width="10.28515625" customWidth="1"/>
-    <col min="2819" max="2819" width="19.42578125" customWidth="1"/>
-    <col min="2820" max="2820" width="9.28515625" customWidth="1"/>
-    <col min="2821" max="2822" width="19.42578125" customWidth="1"/>
-    <col min="3068" max="3068" width="7.28515625" customWidth="1"/>
-    <col min="3069" max="3069" width="19.42578125" customWidth="1"/>
-    <col min="3070" max="3070" width="2.85546875" customWidth="1"/>
-    <col min="3071" max="3071" width="5.5703125" customWidth="1"/>
-    <col min="3072" max="3072" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="3073" max="3073" width="23.28515625" customWidth="1"/>
-    <col min="3074" max="3074" width="10.28515625" customWidth="1"/>
-    <col min="3075" max="3075" width="19.42578125" customWidth="1"/>
-    <col min="3076" max="3076" width="9.28515625" customWidth="1"/>
-    <col min="3077" max="3078" width="19.42578125" customWidth="1"/>
-    <col min="3324" max="3324" width="7.28515625" customWidth="1"/>
-    <col min="3325" max="3325" width="19.42578125" customWidth="1"/>
-    <col min="3326" max="3326" width="2.85546875" customWidth="1"/>
-    <col min="3327" max="3327" width="5.5703125" customWidth="1"/>
-    <col min="3328" max="3328" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="3329" max="3329" width="23.28515625" customWidth="1"/>
-    <col min="3330" max="3330" width="10.28515625" customWidth="1"/>
-    <col min="3331" max="3331" width="19.42578125" customWidth="1"/>
-    <col min="3332" max="3332" width="9.28515625" customWidth="1"/>
-    <col min="3333" max="3334" width="19.42578125" customWidth="1"/>
-    <col min="3580" max="3580" width="7.28515625" customWidth="1"/>
-    <col min="3581" max="3581" width="19.42578125" customWidth="1"/>
-    <col min="3582" max="3582" width="2.85546875" customWidth="1"/>
-    <col min="3583" max="3583" width="5.5703125" customWidth="1"/>
-    <col min="3584" max="3584" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="3585" max="3585" width="23.28515625" customWidth="1"/>
-    <col min="3586" max="3586" width="10.28515625" customWidth="1"/>
-    <col min="3587" max="3587" width="19.42578125" customWidth="1"/>
-    <col min="3588" max="3588" width="9.28515625" customWidth="1"/>
-    <col min="3589" max="3590" width="19.42578125" customWidth="1"/>
-    <col min="3836" max="3836" width="7.28515625" customWidth="1"/>
-    <col min="3837" max="3837" width="19.42578125" customWidth="1"/>
-    <col min="3838" max="3838" width="2.85546875" customWidth="1"/>
-    <col min="3839" max="3839" width="5.5703125" customWidth="1"/>
-    <col min="3840" max="3840" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="3841" max="3841" width="23.28515625" customWidth="1"/>
-    <col min="3842" max="3842" width="10.28515625" customWidth="1"/>
-    <col min="3843" max="3843" width="19.42578125" customWidth="1"/>
-    <col min="3844" max="3844" width="9.28515625" customWidth="1"/>
-    <col min="3845" max="3846" width="19.42578125" customWidth="1"/>
-    <col min="4092" max="4092" width="7.28515625" customWidth="1"/>
-    <col min="4093" max="4093" width="19.42578125" customWidth="1"/>
-    <col min="4094" max="4094" width="2.85546875" customWidth="1"/>
-    <col min="4095" max="4095" width="5.5703125" customWidth="1"/>
-    <col min="4096" max="4096" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="4097" max="4097" width="23.28515625" customWidth="1"/>
-    <col min="4098" max="4098" width="10.28515625" customWidth="1"/>
-    <col min="4099" max="4099" width="19.42578125" customWidth="1"/>
-    <col min="4100" max="4100" width="9.28515625" customWidth="1"/>
-    <col min="4101" max="4102" width="19.42578125" customWidth="1"/>
-    <col min="4348" max="4348" width="7.28515625" customWidth="1"/>
-    <col min="4349" max="4349" width="19.42578125" customWidth="1"/>
-    <col min="4350" max="4350" width="2.85546875" customWidth="1"/>
-    <col min="4351" max="4351" width="5.5703125" customWidth="1"/>
-    <col min="4352" max="4352" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="4353" max="4353" width="23.28515625" customWidth="1"/>
-    <col min="4354" max="4354" width="10.28515625" customWidth="1"/>
-    <col min="4355" max="4355" width="19.42578125" customWidth="1"/>
-    <col min="4356" max="4356" width="9.28515625" customWidth="1"/>
-    <col min="4357" max="4358" width="19.42578125" customWidth="1"/>
-    <col min="4604" max="4604" width="7.28515625" customWidth="1"/>
-    <col min="4605" max="4605" width="19.42578125" customWidth="1"/>
-    <col min="4606" max="4606" width="2.85546875" customWidth="1"/>
-    <col min="4607" max="4607" width="5.5703125" customWidth="1"/>
-    <col min="4608" max="4608" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="4609" max="4609" width="23.28515625" customWidth="1"/>
-    <col min="4610" max="4610" width="10.28515625" customWidth="1"/>
-    <col min="4611" max="4611" width="19.42578125" customWidth="1"/>
-    <col min="4612" max="4612" width="9.28515625" customWidth="1"/>
-    <col min="4613" max="4614" width="19.42578125" customWidth="1"/>
-    <col min="4860" max="4860" width="7.28515625" customWidth="1"/>
-    <col min="4861" max="4861" width="19.42578125" customWidth="1"/>
-    <col min="4862" max="4862" width="2.85546875" customWidth="1"/>
-    <col min="4863" max="4863" width="5.5703125" customWidth="1"/>
-    <col min="4864" max="4864" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="4865" max="4865" width="23.28515625" customWidth="1"/>
-    <col min="4866" max="4866" width="10.28515625" customWidth="1"/>
-    <col min="4867" max="4867" width="19.42578125" customWidth="1"/>
-    <col min="4868" max="4868" width="9.28515625" customWidth="1"/>
-    <col min="4869" max="4870" width="19.42578125" customWidth="1"/>
-    <col min="5116" max="5116" width="7.28515625" customWidth="1"/>
-    <col min="5117" max="5117" width="19.42578125" customWidth="1"/>
-    <col min="5118" max="5118" width="2.85546875" customWidth="1"/>
-    <col min="5119" max="5119" width="5.5703125" customWidth="1"/>
-    <col min="5120" max="5120" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="5121" max="5121" width="23.28515625" customWidth="1"/>
-    <col min="5122" max="5122" width="10.28515625" customWidth="1"/>
-    <col min="5123" max="5123" width="19.42578125" customWidth="1"/>
-    <col min="5124" max="5124" width="9.28515625" customWidth="1"/>
-    <col min="5125" max="5126" width="19.42578125" customWidth="1"/>
-    <col min="5372" max="5372" width="7.28515625" customWidth="1"/>
-    <col min="5373" max="5373" width="19.42578125" customWidth="1"/>
-    <col min="5374" max="5374" width="2.85546875" customWidth="1"/>
-    <col min="5375" max="5375" width="5.5703125" customWidth="1"/>
-    <col min="5376" max="5376" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="5377" max="5377" width="23.28515625" customWidth="1"/>
-    <col min="5378" max="5378" width="10.28515625" customWidth="1"/>
-    <col min="5379" max="5379" width="19.42578125" customWidth="1"/>
-    <col min="5380" max="5380" width="9.28515625" customWidth="1"/>
-    <col min="5381" max="5382" width="19.42578125" customWidth="1"/>
-    <col min="5628" max="5628" width="7.28515625" customWidth="1"/>
-    <col min="5629" max="5629" width="19.42578125" customWidth="1"/>
-    <col min="5630" max="5630" width="2.85546875" customWidth="1"/>
-    <col min="5631" max="5631" width="5.5703125" customWidth="1"/>
-    <col min="5632" max="5632" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="5633" max="5633" width="23.28515625" customWidth="1"/>
-    <col min="5634" max="5634" width="10.28515625" customWidth="1"/>
-    <col min="5635" max="5635" width="19.42578125" customWidth="1"/>
-    <col min="5636" max="5636" width="9.28515625" customWidth="1"/>
-    <col min="5637" max="5638" width="19.42578125" customWidth="1"/>
-    <col min="5884" max="5884" width="7.28515625" customWidth="1"/>
-    <col min="5885" max="5885" width="19.42578125" customWidth="1"/>
-    <col min="5886" max="5886" width="2.85546875" customWidth="1"/>
-    <col min="5887" max="5887" width="5.5703125" customWidth="1"/>
-    <col min="5888" max="5888" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="5889" max="5889" width="23.28515625" customWidth="1"/>
-    <col min="5890" max="5890" width="10.28515625" customWidth="1"/>
-    <col min="5891" max="5891" width="19.42578125" customWidth="1"/>
-    <col min="5892" max="5892" width="9.28515625" customWidth="1"/>
-    <col min="5893" max="5894" width="19.42578125" customWidth="1"/>
-    <col min="6140" max="6140" width="7.28515625" customWidth="1"/>
-    <col min="6141" max="6141" width="19.42578125" customWidth="1"/>
-    <col min="6142" max="6142" width="2.85546875" customWidth="1"/>
-    <col min="6143" max="6143" width="5.5703125" customWidth="1"/>
-    <col min="6144" max="6144" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="6145" max="6145" width="23.28515625" customWidth="1"/>
-    <col min="6146" max="6146" width="10.28515625" customWidth="1"/>
-    <col min="6147" max="6147" width="19.42578125" customWidth="1"/>
-    <col min="6148" max="6148" width="9.28515625" customWidth="1"/>
-    <col min="6149" max="6150" width="19.42578125" customWidth="1"/>
-    <col min="6396" max="6396" width="7.28515625" customWidth="1"/>
-    <col min="6397" max="6397" width="19.42578125" customWidth="1"/>
-    <col min="6398" max="6398" width="2.85546875" customWidth="1"/>
-    <col min="6399" max="6399" width="5.5703125" customWidth="1"/>
-    <col min="6400" max="6400" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="6401" max="6401" width="23.28515625" customWidth="1"/>
-    <col min="6402" max="6402" width="10.28515625" customWidth="1"/>
-    <col min="6403" max="6403" width="19.42578125" customWidth="1"/>
-    <col min="6404" max="6404" width="9.28515625" customWidth="1"/>
-    <col min="6405" max="6406" width="19.42578125" customWidth="1"/>
-    <col min="6652" max="6652" width="7.28515625" customWidth="1"/>
-    <col min="6653" max="6653" width="19.42578125" customWidth="1"/>
-    <col min="6654" max="6654" width="2.85546875" customWidth="1"/>
-    <col min="6655" max="6655" width="5.5703125" customWidth="1"/>
-    <col min="6656" max="6656" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="6657" max="6657" width="23.28515625" customWidth="1"/>
-    <col min="6658" max="6658" width="10.28515625" customWidth="1"/>
-    <col min="6659" max="6659" width="19.42578125" customWidth="1"/>
-    <col min="6660" max="6660" width="9.28515625" customWidth="1"/>
-    <col min="6661" max="6662" width="19.42578125" customWidth="1"/>
-    <col min="6908" max="6908" width="7.28515625" customWidth="1"/>
-    <col min="6909" max="6909" width="19.42578125" customWidth="1"/>
-    <col min="6910" max="6910" width="2.85546875" customWidth="1"/>
-    <col min="6911" max="6911" width="5.5703125" customWidth="1"/>
-    <col min="6912" max="6912" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="6913" max="6913" width="23.28515625" customWidth="1"/>
-    <col min="6914" max="6914" width="10.28515625" customWidth="1"/>
-    <col min="6915" max="6915" width="19.42578125" customWidth="1"/>
-    <col min="6916" max="6916" width="9.28515625" customWidth="1"/>
-    <col min="6917" max="6918" width="19.42578125" customWidth="1"/>
-    <col min="7164" max="7164" width="7.28515625" customWidth="1"/>
-    <col min="7165" max="7165" width="19.42578125" customWidth="1"/>
-    <col min="7166" max="7166" width="2.85546875" customWidth="1"/>
-    <col min="7167" max="7167" width="5.5703125" customWidth="1"/>
-    <col min="7168" max="7168" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="7169" max="7169" width="23.28515625" customWidth="1"/>
-    <col min="7170" max="7170" width="10.28515625" customWidth="1"/>
-    <col min="7171" max="7171" width="19.42578125" customWidth="1"/>
-    <col min="7172" max="7172" width="9.28515625" customWidth="1"/>
-    <col min="7173" max="7174" width="19.42578125" customWidth="1"/>
-    <col min="7420" max="7420" width="7.28515625" customWidth="1"/>
-    <col min="7421" max="7421" width="19.42578125" customWidth="1"/>
-    <col min="7422" max="7422" width="2.85546875" customWidth="1"/>
-    <col min="7423" max="7423" width="5.5703125" customWidth="1"/>
-    <col min="7424" max="7424" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="7425" max="7425" width="23.28515625" customWidth="1"/>
-    <col min="7426" max="7426" width="10.28515625" customWidth="1"/>
-    <col min="7427" max="7427" width="19.42578125" customWidth="1"/>
-    <col min="7428" max="7428" width="9.28515625" customWidth="1"/>
-    <col min="7429" max="7430" width="19.42578125" customWidth="1"/>
-    <col min="7676" max="7676" width="7.28515625" customWidth="1"/>
-    <col min="7677" max="7677" width="19.42578125" customWidth="1"/>
-    <col min="7678" max="7678" width="2.85546875" customWidth="1"/>
-    <col min="7679" max="7679" width="5.5703125" customWidth="1"/>
-    <col min="7680" max="7680" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="7681" max="7681" width="23.28515625" customWidth="1"/>
-    <col min="7682" max="7682" width="10.28515625" customWidth="1"/>
-    <col min="7683" max="7683" width="19.42578125" customWidth="1"/>
-    <col min="7684" max="7684" width="9.28515625" customWidth="1"/>
-    <col min="7685" max="7686" width="19.42578125" customWidth="1"/>
-    <col min="7932" max="7932" width="7.28515625" customWidth="1"/>
-    <col min="7933" max="7933" width="19.42578125" customWidth="1"/>
-    <col min="7934" max="7934" width="2.85546875" customWidth="1"/>
-    <col min="7935" max="7935" width="5.5703125" customWidth="1"/>
-    <col min="7936" max="7936" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="7937" max="7937" width="23.28515625" customWidth="1"/>
-    <col min="7938" max="7938" width="10.28515625" customWidth="1"/>
-    <col min="7939" max="7939" width="19.42578125" customWidth="1"/>
-    <col min="7940" max="7940" width="9.28515625" customWidth="1"/>
-    <col min="7941" max="7942" width="19.42578125" customWidth="1"/>
-    <col min="8188" max="8188" width="7.28515625" customWidth="1"/>
-    <col min="8189" max="8189" width="19.42578125" customWidth="1"/>
-    <col min="8190" max="8190" width="2.85546875" customWidth="1"/>
-    <col min="8191" max="8191" width="5.5703125" customWidth="1"/>
-    <col min="8192" max="8192" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="8193" max="8193" width="23.28515625" customWidth="1"/>
-    <col min="8194" max="8194" width="10.28515625" customWidth="1"/>
-    <col min="8195" max="8195" width="19.42578125" customWidth="1"/>
-    <col min="8196" max="8196" width="9.28515625" customWidth="1"/>
-    <col min="8197" max="8198" width="19.42578125" customWidth="1"/>
-    <col min="8444" max="8444" width="7.28515625" customWidth="1"/>
-    <col min="8445" max="8445" width="19.42578125" customWidth="1"/>
-    <col min="8446" max="8446" width="2.85546875" customWidth="1"/>
-    <col min="8447" max="8447" width="5.5703125" customWidth="1"/>
-    <col min="8448" max="8448" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="8449" max="8449" width="23.28515625" customWidth="1"/>
-    <col min="8450" max="8450" width="10.28515625" customWidth="1"/>
-    <col min="8451" max="8451" width="19.42578125" customWidth="1"/>
-    <col min="8452" max="8452" width="9.28515625" customWidth="1"/>
-    <col min="8453" max="8454" width="19.42578125" customWidth="1"/>
-    <col min="8700" max="8700" width="7.28515625" customWidth="1"/>
-    <col min="8701" max="8701" width="19.42578125" customWidth="1"/>
-    <col min="8702" max="8702" width="2.85546875" customWidth="1"/>
-    <col min="8703" max="8703" width="5.5703125" customWidth="1"/>
-    <col min="8704" max="8704" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="8705" max="8705" width="23.28515625" customWidth="1"/>
-    <col min="8706" max="8706" width="10.28515625" customWidth="1"/>
-    <col min="8707" max="8707" width="19.42578125" customWidth="1"/>
-    <col min="8708" max="8708" width="9.28515625" customWidth="1"/>
-    <col min="8709" max="8710" width="19.42578125" customWidth="1"/>
-    <col min="8956" max="8956" width="7.28515625" customWidth="1"/>
-    <col min="8957" max="8957" width="19.42578125" customWidth="1"/>
-    <col min="8958" max="8958" width="2.85546875" customWidth="1"/>
-    <col min="8959" max="8959" width="5.5703125" customWidth="1"/>
-    <col min="8960" max="8960" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="8961" max="8961" width="23.28515625" customWidth="1"/>
-    <col min="8962" max="8962" width="10.28515625" customWidth="1"/>
-    <col min="8963" max="8963" width="19.42578125" customWidth="1"/>
-    <col min="8964" max="8964" width="9.28515625" customWidth="1"/>
-    <col min="8965" max="8966" width="19.42578125" customWidth="1"/>
-    <col min="9212" max="9212" width="7.28515625" customWidth="1"/>
-    <col min="9213" max="9213" width="19.42578125" customWidth="1"/>
-    <col min="9214" max="9214" width="2.85546875" customWidth="1"/>
-    <col min="9215" max="9215" width="5.5703125" customWidth="1"/>
-    <col min="9216" max="9216" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="9217" max="9217" width="23.28515625" customWidth="1"/>
-    <col min="9218" max="9218" width="10.28515625" customWidth="1"/>
-    <col min="9219" max="9219" width="19.42578125" customWidth="1"/>
-    <col min="9220" max="9220" width="9.28515625" customWidth="1"/>
-    <col min="9221" max="9222" width="19.42578125" customWidth="1"/>
-    <col min="9468" max="9468" width="7.28515625" customWidth="1"/>
-    <col min="9469" max="9469" width="19.42578125" customWidth="1"/>
-    <col min="9470" max="9470" width="2.85546875" customWidth="1"/>
-    <col min="9471" max="9471" width="5.5703125" customWidth="1"/>
-    <col min="9472" max="9472" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="9473" max="9473" width="23.28515625" customWidth="1"/>
-    <col min="9474" max="9474" width="10.28515625" customWidth="1"/>
-    <col min="9475" max="9475" width="19.42578125" customWidth="1"/>
-    <col min="9476" max="9476" width="9.28515625" customWidth="1"/>
-    <col min="9477" max="9478" width="19.42578125" customWidth="1"/>
-    <col min="9724" max="9724" width="7.28515625" customWidth="1"/>
-    <col min="9725" max="9725" width="19.42578125" customWidth="1"/>
-    <col min="9726" max="9726" width="2.85546875" customWidth="1"/>
-    <col min="9727" max="9727" width="5.5703125" customWidth="1"/>
-    <col min="9728" max="9728" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="9729" max="9729" width="23.28515625" customWidth="1"/>
-    <col min="9730" max="9730" width="10.28515625" customWidth="1"/>
-    <col min="9731" max="9731" width="19.42578125" customWidth="1"/>
-    <col min="9732" max="9732" width="9.28515625" customWidth="1"/>
-    <col min="9733" max="9734" width="19.42578125" customWidth="1"/>
-    <col min="9980" max="9980" width="7.28515625" customWidth="1"/>
-    <col min="9981" max="9981" width="19.42578125" customWidth="1"/>
-    <col min="9982" max="9982" width="2.85546875" customWidth="1"/>
-    <col min="9983" max="9983" width="5.5703125" customWidth="1"/>
-    <col min="9984" max="9984" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="9985" max="9985" width="23.28515625" customWidth="1"/>
-    <col min="9986" max="9986" width="10.28515625" customWidth="1"/>
-    <col min="9987" max="9987" width="19.42578125" customWidth="1"/>
-    <col min="9988" max="9988" width="9.28515625" customWidth="1"/>
-    <col min="9989" max="9990" width="19.42578125" customWidth="1"/>
-    <col min="10236" max="10236" width="7.28515625" customWidth="1"/>
-    <col min="10237" max="10237" width="19.42578125" customWidth="1"/>
-    <col min="10238" max="10238" width="2.85546875" customWidth="1"/>
-    <col min="10239" max="10239" width="5.5703125" customWidth="1"/>
-    <col min="10240" max="10240" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="10241" max="10241" width="23.28515625" customWidth="1"/>
-    <col min="10242" max="10242" width="10.28515625" customWidth="1"/>
-    <col min="10243" max="10243" width="19.42578125" customWidth="1"/>
-    <col min="10244" max="10244" width="9.28515625" customWidth="1"/>
-    <col min="10245" max="10246" width="19.42578125" customWidth="1"/>
-    <col min="10492" max="10492" width="7.28515625" customWidth="1"/>
-    <col min="10493" max="10493" width="19.42578125" customWidth="1"/>
-    <col min="10494" max="10494" width="2.85546875" customWidth="1"/>
-    <col min="10495" max="10495" width="5.5703125" customWidth="1"/>
-    <col min="10496" max="10496" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="10497" max="10497" width="23.28515625" customWidth="1"/>
-    <col min="10498" max="10498" width="10.28515625" customWidth="1"/>
-    <col min="10499" max="10499" width="19.42578125" customWidth="1"/>
-    <col min="10500" max="10500" width="9.28515625" customWidth="1"/>
-    <col min="10501" max="10502" width="19.42578125" customWidth="1"/>
-    <col min="10748" max="10748" width="7.28515625" customWidth="1"/>
-    <col min="10749" max="10749" width="19.42578125" customWidth="1"/>
-    <col min="10750" max="10750" width="2.85546875" customWidth="1"/>
-    <col min="10751" max="10751" width="5.5703125" customWidth="1"/>
-    <col min="10752" max="10752" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="10753" max="10753" width="23.28515625" customWidth="1"/>
-    <col min="10754" max="10754" width="10.28515625" customWidth="1"/>
-    <col min="10755" max="10755" width="19.42578125" customWidth="1"/>
-    <col min="10756" max="10756" width="9.28515625" customWidth="1"/>
-    <col min="10757" max="10758" width="19.42578125" customWidth="1"/>
-    <col min="11004" max="11004" width="7.28515625" customWidth="1"/>
-    <col min="11005" max="11005" width="19.42578125" customWidth="1"/>
-    <col min="11006" max="11006" width="2.85546875" customWidth="1"/>
-    <col min="11007" max="11007" width="5.5703125" customWidth="1"/>
-    <col min="11008" max="11008" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="11009" max="11009" width="23.28515625" customWidth="1"/>
-    <col min="11010" max="11010" width="10.28515625" customWidth="1"/>
-    <col min="11011" max="11011" width="19.42578125" customWidth="1"/>
-    <col min="11012" max="11012" width="9.28515625" customWidth="1"/>
-    <col min="11013" max="11014" width="19.42578125" customWidth="1"/>
-    <col min="11260" max="11260" width="7.28515625" customWidth="1"/>
-    <col min="11261" max="11261" width="19.42578125" customWidth="1"/>
-    <col min="11262" max="11262" width="2.85546875" customWidth="1"/>
-    <col min="11263" max="11263" width="5.5703125" customWidth="1"/>
-    <col min="11264" max="11264" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="11265" max="11265" width="23.28515625" customWidth="1"/>
-    <col min="11266" max="11266" width="10.28515625" customWidth="1"/>
-    <col min="11267" max="11267" width="19.42578125" customWidth="1"/>
-    <col min="11268" max="11268" width="9.28515625" customWidth="1"/>
-    <col min="11269" max="11270" width="19.42578125" customWidth="1"/>
-    <col min="11516" max="11516" width="7.28515625" customWidth="1"/>
-    <col min="11517" max="11517" width="19.42578125" customWidth="1"/>
-    <col min="11518" max="11518" width="2.85546875" customWidth="1"/>
-    <col min="11519" max="11519" width="5.5703125" customWidth="1"/>
-    <col min="11520" max="11520" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="11521" max="11521" width="23.28515625" customWidth="1"/>
-    <col min="11522" max="11522" width="10.28515625" customWidth="1"/>
-    <col min="11523" max="11523" width="19.42578125" customWidth="1"/>
-    <col min="11524" max="11524" width="9.28515625" customWidth="1"/>
-    <col min="11525" max="11526" width="19.42578125" customWidth="1"/>
-    <col min="11772" max="11772" width="7.28515625" customWidth="1"/>
-    <col min="11773" max="11773" width="19.42578125" customWidth="1"/>
-    <col min="11774" max="11774" width="2.85546875" customWidth="1"/>
-    <col min="11775" max="11775" width="5.5703125" customWidth="1"/>
-    <col min="11776" max="11776" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="11777" max="11777" width="23.28515625" customWidth="1"/>
-    <col min="11778" max="11778" width="10.28515625" customWidth="1"/>
-    <col min="11779" max="11779" width="19.42578125" customWidth="1"/>
-    <col min="11780" max="11780" width="9.28515625" customWidth="1"/>
-    <col min="11781" max="11782" width="19.42578125" customWidth="1"/>
-    <col min="12028" max="12028" width="7.28515625" customWidth="1"/>
-    <col min="12029" max="12029" width="19.42578125" customWidth="1"/>
-    <col min="12030" max="12030" width="2.85546875" customWidth="1"/>
-    <col min="12031" max="12031" width="5.5703125" customWidth="1"/>
-    <col min="12032" max="12032" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="12033" max="12033" width="23.28515625" customWidth="1"/>
-    <col min="12034" max="12034" width="10.28515625" customWidth="1"/>
-    <col min="12035" max="12035" width="19.42578125" customWidth="1"/>
-    <col min="12036" max="12036" width="9.28515625" customWidth="1"/>
-    <col min="12037" max="12038" width="19.42578125" customWidth="1"/>
-    <col min="12284" max="12284" width="7.28515625" customWidth="1"/>
-    <col min="12285" max="12285" width="19.42578125" customWidth="1"/>
-    <col min="12286" max="12286" width="2.85546875" customWidth="1"/>
-    <col min="12287" max="12287" width="5.5703125" customWidth="1"/>
-    <col min="12288" max="12288" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="12289" max="12289" width="23.28515625" customWidth="1"/>
-    <col min="12290" max="12290" width="10.28515625" customWidth="1"/>
-    <col min="12291" max="12291" width="19.42578125" customWidth="1"/>
-    <col min="12292" max="12292" width="9.28515625" customWidth="1"/>
-    <col min="12293" max="12294" width="19.42578125" customWidth="1"/>
-    <col min="12540" max="12540" width="7.28515625" customWidth="1"/>
-    <col min="12541" max="12541" width="19.42578125" customWidth="1"/>
-    <col min="12542" max="12542" width="2.85546875" customWidth="1"/>
-    <col min="12543" max="12543" width="5.5703125" customWidth="1"/>
-    <col min="12544" max="12544" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="12545" max="12545" width="23.28515625" customWidth="1"/>
-    <col min="12546" max="12546" width="10.28515625" customWidth="1"/>
-    <col min="12547" max="12547" width="19.42578125" customWidth="1"/>
-    <col min="12548" max="12548" width="9.28515625" customWidth="1"/>
-    <col min="12549" max="12550" width="19.42578125" customWidth="1"/>
-    <col min="12796" max="12796" width="7.28515625" customWidth="1"/>
-    <col min="12797" max="12797" width="19.42578125" customWidth="1"/>
-    <col min="12798" max="12798" width="2.85546875" customWidth="1"/>
-    <col min="12799" max="12799" width="5.5703125" customWidth="1"/>
-    <col min="12800" max="12800" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="12801" max="12801" width="23.28515625" customWidth="1"/>
-    <col min="12802" max="12802" width="10.28515625" customWidth="1"/>
-    <col min="12803" max="12803" width="19.42578125" customWidth="1"/>
-    <col min="12804" max="12804" width="9.28515625" customWidth="1"/>
-    <col min="12805" max="12806" width="19.42578125" customWidth="1"/>
-    <col min="13052" max="13052" width="7.28515625" customWidth="1"/>
-    <col min="13053" max="13053" width="19.42578125" customWidth="1"/>
-    <col min="13054" max="13054" width="2.85546875" customWidth="1"/>
-    <col min="13055" max="13055" width="5.5703125" customWidth="1"/>
-    <col min="13056" max="13056" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="13057" max="13057" width="23.28515625" customWidth="1"/>
-    <col min="13058" max="13058" width="10.28515625" customWidth="1"/>
-    <col min="13059" max="13059" width="19.42578125" customWidth="1"/>
-    <col min="13060" max="13060" width="9.28515625" customWidth="1"/>
-    <col min="13061" max="13062" width="19.42578125" customWidth="1"/>
-    <col min="13308" max="13308" width="7.28515625" customWidth="1"/>
-    <col min="13309" max="13309" width="19.42578125" customWidth="1"/>
-    <col min="13310" max="13310" width="2.85546875" customWidth="1"/>
-    <col min="13311" max="13311" width="5.5703125" customWidth="1"/>
-    <col min="13312" max="13312" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="13313" max="13313" width="23.28515625" customWidth="1"/>
-    <col min="13314" max="13314" width="10.28515625" customWidth="1"/>
-    <col min="13315" max="13315" width="19.42578125" customWidth="1"/>
-    <col min="13316" max="13316" width="9.28515625" customWidth="1"/>
-    <col min="13317" max="13318" width="19.42578125" customWidth="1"/>
-    <col min="13564" max="13564" width="7.28515625" customWidth="1"/>
-    <col min="13565" max="13565" width="19.42578125" customWidth="1"/>
-    <col min="13566" max="13566" width="2.85546875" customWidth="1"/>
-    <col min="13567" max="13567" width="5.5703125" customWidth="1"/>
-    <col min="13568" max="13568" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="13569" max="13569" width="23.28515625" customWidth="1"/>
-    <col min="13570" max="13570" width="10.28515625" customWidth="1"/>
-    <col min="13571" max="13571" width="19.42578125" customWidth="1"/>
-    <col min="13572" max="13572" width="9.28515625" customWidth="1"/>
-    <col min="13573" max="13574" width="19.42578125" customWidth="1"/>
-    <col min="13820" max="13820" width="7.28515625" customWidth="1"/>
-    <col min="13821" max="13821" width="19.42578125" customWidth="1"/>
-    <col min="13822" max="13822" width="2.85546875" customWidth="1"/>
-    <col min="13823" max="13823" width="5.5703125" customWidth="1"/>
-    <col min="13824" max="13824" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="13825" max="13825" width="23.28515625" customWidth="1"/>
-    <col min="13826" max="13826" width="10.28515625" customWidth="1"/>
-    <col min="13827" max="13827" width="19.42578125" customWidth="1"/>
-    <col min="13828" max="13828" width="9.28515625" customWidth="1"/>
-    <col min="13829" max="13830" width="19.42578125" customWidth="1"/>
-    <col min="14076" max="14076" width="7.28515625" customWidth="1"/>
-    <col min="14077" max="14077" width="19.42578125" customWidth="1"/>
-    <col min="14078" max="14078" width="2.85546875" customWidth="1"/>
-    <col min="14079" max="14079" width="5.5703125" customWidth="1"/>
-    <col min="14080" max="14080" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="14081" max="14081" width="23.28515625" customWidth="1"/>
-    <col min="14082" max="14082" width="10.28515625" customWidth="1"/>
-    <col min="14083" max="14083" width="19.42578125" customWidth="1"/>
-    <col min="14084" max="14084" width="9.28515625" customWidth="1"/>
-    <col min="14085" max="14086" width="19.42578125" customWidth="1"/>
-    <col min="14332" max="14332" width="7.28515625" customWidth="1"/>
-    <col min="14333" max="14333" width="19.42578125" customWidth="1"/>
-    <col min="14334" max="14334" width="2.85546875" customWidth="1"/>
-    <col min="14335" max="14335" width="5.5703125" customWidth="1"/>
-    <col min="14336" max="14336" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="14337" max="14337" width="23.28515625" customWidth="1"/>
-    <col min="14338" max="14338" width="10.28515625" customWidth="1"/>
-    <col min="14339" max="14339" width="19.42578125" customWidth="1"/>
-    <col min="14340" max="14340" width="9.28515625" customWidth="1"/>
-    <col min="14341" max="14342" width="19.42578125" customWidth="1"/>
-    <col min="14588" max="14588" width="7.28515625" customWidth="1"/>
-    <col min="14589" max="14589" width="19.42578125" customWidth="1"/>
-    <col min="14590" max="14590" width="2.85546875" customWidth="1"/>
-    <col min="14591" max="14591" width="5.5703125" customWidth="1"/>
-    <col min="14592" max="14592" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="14593" max="14593" width="23.28515625" customWidth="1"/>
-    <col min="14594" max="14594" width="10.28515625" customWidth="1"/>
-    <col min="14595" max="14595" width="19.42578125" customWidth="1"/>
-    <col min="14596" max="14596" width="9.28515625" customWidth="1"/>
-    <col min="14597" max="14598" width="19.42578125" customWidth="1"/>
-    <col min="14844" max="14844" width="7.28515625" customWidth="1"/>
-    <col min="14845" max="14845" width="19.42578125" customWidth="1"/>
-    <col min="14846" max="14846" width="2.85546875" customWidth="1"/>
-    <col min="14847" max="14847" width="5.5703125" customWidth="1"/>
-    <col min="14848" max="14848" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="14849" max="14849" width="23.28515625" customWidth="1"/>
-    <col min="14850" max="14850" width="10.28515625" customWidth="1"/>
-    <col min="14851" max="14851" width="19.42578125" customWidth="1"/>
-    <col min="14852" max="14852" width="9.28515625" customWidth="1"/>
-    <col min="14853" max="14854" width="19.42578125" customWidth="1"/>
-    <col min="15100" max="15100" width="7.28515625" customWidth="1"/>
-    <col min="15101" max="15101" width="19.42578125" customWidth="1"/>
-    <col min="15102" max="15102" width="2.85546875" customWidth="1"/>
-    <col min="15103" max="15103" width="5.5703125" customWidth="1"/>
-    <col min="15104" max="15104" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="15105" max="15105" width="23.28515625" customWidth="1"/>
-    <col min="15106" max="15106" width="10.28515625" customWidth="1"/>
-    <col min="15107" max="15107" width="19.42578125" customWidth="1"/>
-    <col min="15108" max="15108" width="9.28515625" customWidth="1"/>
-    <col min="15109" max="15110" width="19.42578125" customWidth="1"/>
-    <col min="15356" max="15356" width="7.28515625" customWidth="1"/>
-    <col min="15357" max="15357" width="19.42578125" customWidth="1"/>
-    <col min="15358" max="15358" width="2.85546875" customWidth="1"/>
-    <col min="15359" max="15359" width="5.5703125" customWidth="1"/>
-    <col min="15360" max="15360" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="15361" max="15361" width="23.28515625" customWidth="1"/>
-    <col min="15362" max="15362" width="10.28515625" customWidth="1"/>
-    <col min="15363" max="15363" width="19.42578125" customWidth="1"/>
-    <col min="15364" max="15364" width="9.28515625" customWidth="1"/>
-    <col min="15365" max="15366" width="19.42578125" customWidth="1"/>
-    <col min="15612" max="15612" width="7.28515625" customWidth="1"/>
-    <col min="15613" max="15613" width="19.42578125" customWidth="1"/>
-    <col min="15614" max="15614" width="2.85546875" customWidth="1"/>
-    <col min="15615" max="15615" width="5.5703125" customWidth="1"/>
-    <col min="15616" max="15616" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="15617" max="15617" width="23.28515625" customWidth="1"/>
-    <col min="15618" max="15618" width="10.28515625" customWidth="1"/>
-    <col min="15619" max="15619" width="19.42578125" customWidth="1"/>
-    <col min="15620" max="15620" width="9.28515625" customWidth="1"/>
-    <col min="15621" max="15622" width="19.42578125" customWidth="1"/>
-    <col min="15868" max="15868" width="7.28515625" customWidth="1"/>
-    <col min="15869" max="15869" width="19.42578125" customWidth="1"/>
-    <col min="15870" max="15870" width="2.85546875" customWidth="1"/>
-    <col min="15871" max="15871" width="5.5703125" customWidth="1"/>
-    <col min="15872" max="15872" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="15873" max="15873" width="23.28515625" customWidth="1"/>
-    <col min="15874" max="15874" width="10.28515625" customWidth="1"/>
-    <col min="15875" max="15875" width="19.42578125" customWidth="1"/>
-    <col min="15876" max="15876" width="9.28515625" customWidth="1"/>
-    <col min="15877" max="15878" width="19.42578125" customWidth="1"/>
-    <col min="16124" max="16124" width="7.28515625" customWidth="1"/>
-    <col min="16125" max="16125" width="19.42578125" customWidth="1"/>
-    <col min="16126" max="16126" width="2.85546875" customWidth="1"/>
-    <col min="16127" max="16127" width="5.5703125" customWidth="1"/>
-    <col min="16128" max="16128" width="90.28515625" bestFit="1" customWidth="1"/>
-    <col min="16129" max="16129" width="23.28515625" customWidth="1"/>
-    <col min="16130" max="16130" width="10.28515625" customWidth="1"/>
-    <col min="16131" max="16131" width="19.42578125" customWidth="1"/>
-    <col min="16132" max="16132" width="9.28515625" customWidth="1"/>
-    <col min="16133" max="16134" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="42.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="5" max="5" width="34.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" customWidth="1"/>
+    <col min="7" max="7" width="8.44140625" customWidth="1"/>
+    <col min="252" max="252" width="7.33203125" customWidth="1"/>
+    <col min="253" max="253" width="19.44140625" customWidth="1"/>
+    <col min="254" max="254" width="2.88671875" customWidth="1"/>
+    <col min="255" max="255" width="5.5546875" customWidth="1"/>
+    <col min="256" max="256" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="257" max="257" width="23.33203125" customWidth="1"/>
+    <col min="258" max="258" width="10.33203125" customWidth="1"/>
+    <col min="259" max="259" width="19.44140625" customWidth="1"/>
+    <col min="260" max="260" width="9.33203125" customWidth="1"/>
+    <col min="261" max="262" width="19.44140625" customWidth="1"/>
+    <col min="508" max="508" width="7.33203125" customWidth="1"/>
+    <col min="509" max="509" width="19.44140625" customWidth="1"/>
+    <col min="510" max="510" width="2.88671875" customWidth="1"/>
+    <col min="511" max="511" width="5.5546875" customWidth="1"/>
+    <col min="512" max="512" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="513" max="513" width="23.33203125" customWidth="1"/>
+    <col min="514" max="514" width="10.33203125" customWidth="1"/>
+    <col min="515" max="515" width="19.44140625" customWidth="1"/>
+    <col min="516" max="516" width="9.33203125" customWidth="1"/>
+    <col min="517" max="518" width="19.44140625" customWidth="1"/>
+    <col min="764" max="764" width="7.33203125" customWidth="1"/>
+    <col min="765" max="765" width="19.44140625" customWidth="1"/>
+    <col min="766" max="766" width="2.88671875" customWidth="1"/>
+    <col min="767" max="767" width="5.5546875" customWidth="1"/>
+    <col min="768" max="768" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="769" max="769" width="23.33203125" customWidth="1"/>
+    <col min="770" max="770" width="10.33203125" customWidth="1"/>
+    <col min="771" max="771" width="19.44140625" customWidth="1"/>
+    <col min="772" max="772" width="9.33203125" customWidth="1"/>
+    <col min="773" max="774" width="19.44140625" customWidth="1"/>
+    <col min="1020" max="1020" width="7.33203125" customWidth="1"/>
+    <col min="1021" max="1021" width="19.44140625" customWidth="1"/>
+    <col min="1022" max="1022" width="2.88671875" customWidth="1"/>
+    <col min="1023" max="1023" width="5.5546875" customWidth="1"/>
+    <col min="1024" max="1024" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="1025" max="1025" width="23.33203125" customWidth="1"/>
+    <col min="1026" max="1026" width="10.33203125" customWidth="1"/>
+    <col min="1027" max="1027" width="19.44140625" customWidth="1"/>
+    <col min="1028" max="1028" width="9.33203125" customWidth="1"/>
+    <col min="1029" max="1030" width="19.44140625" customWidth="1"/>
+    <col min="1276" max="1276" width="7.33203125" customWidth="1"/>
+    <col min="1277" max="1277" width="19.44140625" customWidth="1"/>
+    <col min="1278" max="1278" width="2.88671875" customWidth="1"/>
+    <col min="1279" max="1279" width="5.5546875" customWidth="1"/>
+    <col min="1280" max="1280" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="1281" max="1281" width="23.33203125" customWidth="1"/>
+    <col min="1282" max="1282" width="10.33203125" customWidth="1"/>
+    <col min="1283" max="1283" width="19.44140625" customWidth="1"/>
+    <col min="1284" max="1284" width="9.33203125" customWidth="1"/>
+    <col min="1285" max="1286" width="19.44140625" customWidth="1"/>
+    <col min="1532" max="1532" width="7.33203125" customWidth="1"/>
+    <col min="1533" max="1533" width="19.44140625" customWidth="1"/>
+    <col min="1534" max="1534" width="2.88671875" customWidth="1"/>
+    <col min="1535" max="1535" width="5.5546875" customWidth="1"/>
+    <col min="1536" max="1536" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="1537" max="1537" width="23.33203125" customWidth="1"/>
+    <col min="1538" max="1538" width="10.33203125" customWidth="1"/>
+    <col min="1539" max="1539" width="19.44140625" customWidth="1"/>
+    <col min="1540" max="1540" width="9.33203125" customWidth="1"/>
+    <col min="1541" max="1542" width="19.44140625" customWidth="1"/>
+    <col min="1788" max="1788" width="7.33203125" customWidth="1"/>
+    <col min="1789" max="1789" width="19.44140625" customWidth="1"/>
+    <col min="1790" max="1790" width="2.88671875" customWidth="1"/>
+    <col min="1791" max="1791" width="5.5546875" customWidth="1"/>
+    <col min="1792" max="1792" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="1793" max="1793" width="23.33203125" customWidth="1"/>
+    <col min="1794" max="1794" width="10.33203125" customWidth="1"/>
+    <col min="1795" max="1795" width="19.44140625" customWidth="1"/>
+    <col min="1796" max="1796" width="9.33203125" customWidth="1"/>
+    <col min="1797" max="1798" width="19.44140625" customWidth="1"/>
+    <col min="2044" max="2044" width="7.33203125" customWidth="1"/>
+    <col min="2045" max="2045" width="19.44140625" customWidth="1"/>
+    <col min="2046" max="2046" width="2.88671875" customWidth="1"/>
+    <col min="2047" max="2047" width="5.5546875" customWidth="1"/>
+    <col min="2048" max="2048" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="2049" max="2049" width="23.33203125" customWidth="1"/>
+    <col min="2050" max="2050" width="10.33203125" customWidth="1"/>
+    <col min="2051" max="2051" width="19.44140625" customWidth="1"/>
+    <col min="2052" max="2052" width="9.33203125" customWidth="1"/>
+    <col min="2053" max="2054" width="19.44140625" customWidth="1"/>
+    <col min="2300" max="2300" width="7.33203125" customWidth="1"/>
+    <col min="2301" max="2301" width="19.44140625" customWidth="1"/>
+    <col min="2302" max="2302" width="2.88671875" customWidth="1"/>
+    <col min="2303" max="2303" width="5.5546875" customWidth="1"/>
+    <col min="2304" max="2304" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="2305" max="2305" width="23.33203125" customWidth="1"/>
+    <col min="2306" max="2306" width="10.33203125" customWidth="1"/>
+    <col min="2307" max="2307" width="19.44140625" customWidth="1"/>
+    <col min="2308" max="2308" width="9.33203125" customWidth="1"/>
+    <col min="2309" max="2310" width="19.44140625" customWidth="1"/>
+    <col min="2556" max="2556" width="7.33203125" customWidth="1"/>
+    <col min="2557" max="2557" width="19.44140625" customWidth="1"/>
+    <col min="2558" max="2558" width="2.88671875" customWidth="1"/>
+    <col min="2559" max="2559" width="5.5546875" customWidth="1"/>
+    <col min="2560" max="2560" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="2561" max="2561" width="23.33203125" customWidth="1"/>
+    <col min="2562" max="2562" width="10.33203125" customWidth="1"/>
+    <col min="2563" max="2563" width="19.44140625" customWidth="1"/>
+    <col min="2564" max="2564" width="9.33203125" customWidth="1"/>
+    <col min="2565" max="2566" width="19.44140625" customWidth="1"/>
+    <col min="2812" max="2812" width="7.33203125" customWidth="1"/>
+    <col min="2813" max="2813" width="19.44140625" customWidth="1"/>
+    <col min="2814" max="2814" width="2.88671875" customWidth="1"/>
+    <col min="2815" max="2815" width="5.5546875" customWidth="1"/>
+    <col min="2816" max="2816" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="2817" max="2817" width="23.33203125" customWidth="1"/>
+    <col min="2818" max="2818" width="10.33203125" customWidth="1"/>
+    <col min="2819" max="2819" width="19.44140625" customWidth="1"/>
+    <col min="2820" max="2820" width="9.33203125" customWidth="1"/>
+    <col min="2821" max="2822" width="19.44140625" customWidth="1"/>
+    <col min="3068" max="3068" width="7.33203125" customWidth="1"/>
+    <col min="3069" max="3069" width="19.44140625" customWidth="1"/>
+    <col min="3070" max="3070" width="2.88671875" customWidth="1"/>
+    <col min="3071" max="3071" width="5.5546875" customWidth="1"/>
+    <col min="3072" max="3072" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="3073" max="3073" width="23.33203125" customWidth="1"/>
+    <col min="3074" max="3074" width="10.33203125" customWidth="1"/>
+    <col min="3075" max="3075" width="19.44140625" customWidth="1"/>
+    <col min="3076" max="3076" width="9.33203125" customWidth="1"/>
+    <col min="3077" max="3078" width="19.44140625" customWidth="1"/>
+    <col min="3324" max="3324" width="7.33203125" customWidth="1"/>
+    <col min="3325" max="3325" width="19.44140625" customWidth="1"/>
+    <col min="3326" max="3326" width="2.88671875" customWidth="1"/>
+    <col min="3327" max="3327" width="5.5546875" customWidth="1"/>
+    <col min="3328" max="3328" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="3329" max="3329" width="23.33203125" customWidth="1"/>
+    <col min="3330" max="3330" width="10.33203125" customWidth="1"/>
+    <col min="3331" max="3331" width="19.44140625" customWidth="1"/>
+    <col min="3332" max="3332" width="9.33203125" customWidth="1"/>
+    <col min="3333" max="3334" width="19.44140625" customWidth="1"/>
+    <col min="3580" max="3580" width="7.33203125" customWidth="1"/>
+    <col min="3581" max="3581" width="19.44140625" customWidth="1"/>
+    <col min="3582" max="3582" width="2.88671875" customWidth="1"/>
+    <col min="3583" max="3583" width="5.5546875" customWidth="1"/>
+    <col min="3584" max="3584" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="3585" max="3585" width="23.33203125" customWidth="1"/>
+    <col min="3586" max="3586" width="10.33203125" customWidth="1"/>
+    <col min="3587" max="3587" width="19.44140625" customWidth="1"/>
+    <col min="3588" max="3588" width="9.33203125" customWidth="1"/>
+    <col min="3589" max="3590" width="19.44140625" customWidth="1"/>
+    <col min="3836" max="3836" width="7.33203125" customWidth="1"/>
+    <col min="3837" max="3837" width="19.44140625" customWidth="1"/>
+    <col min="3838" max="3838" width="2.88671875" customWidth="1"/>
+    <col min="3839" max="3839" width="5.5546875" customWidth="1"/>
+    <col min="3840" max="3840" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="3841" max="3841" width="23.33203125" customWidth="1"/>
+    <col min="3842" max="3842" width="10.33203125" customWidth="1"/>
+    <col min="3843" max="3843" width="19.44140625" customWidth="1"/>
+    <col min="3844" max="3844" width="9.33203125" customWidth="1"/>
+    <col min="3845" max="3846" width="19.44140625" customWidth="1"/>
+    <col min="4092" max="4092" width="7.33203125" customWidth="1"/>
+    <col min="4093" max="4093" width="19.44140625" customWidth="1"/>
+    <col min="4094" max="4094" width="2.88671875" customWidth="1"/>
+    <col min="4095" max="4095" width="5.5546875" customWidth="1"/>
+    <col min="4096" max="4096" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="4097" max="4097" width="23.33203125" customWidth="1"/>
+    <col min="4098" max="4098" width="10.33203125" customWidth="1"/>
+    <col min="4099" max="4099" width="19.44140625" customWidth="1"/>
+    <col min="4100" max="4100" width="9.33203125" customWidth="1"/>
+    <col min="4101" max="4102" width="19.44140625" customWidth="1"/>
+    <col min="4348" max="4348" width="7.33203125" customWidth="1"/>
+    <col min="4349" max="4349" width="19.44140625" customWidth="1"/>
+    <col min="4350" max="4350" width="2.88671875" customWidth="1"/>
+    <col min="4351" max="4351" width="5.5546875" customWidth="1"/>
+    <col min="4352" max="4352" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="4353" max="4353" width="23.33203125" customWidth="1"/>
+    <col min="4354" max="4354" width="10.33203125" customWidth="1"/>
+    <col min="4355" max="4355" width="19.44140625" customWidth="1"/>
+    <col min="4356" max="4356" width="9.33203125" customWidth="1"/>
+    <col min="4357" max="4358" width="19.44140625" customWidth="1"/>
+    <col min="4604" max="4604" width="7.33203125" customWidth="1"/>
+    <col min="4605" max="4605" width="19.44140625" customWidth="1"/>
+    <col min="4606" max="4606" width="2.88671875" customWidth="1"/>
+    <col min="4607" max="4607" width="5.5546875" customWidth="1"/>
+    <col min="4608" max="4608" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="4609" max="4609" width="23.33203125" customWidth="1"/>
+    <col min="4610" max="4610" width="10.33203125" customWidth="1"/>
+    <col min="4611" max="4611" width="19.44140625" customWidth="1"/>
+    <col min="4612" max="4612" width="9.33203125" customWidth="1"/>
+    <col min="4613" max="4614" width="19.44140625" customWidth="1"/>
+    <col min="4860" max="4860" width="7.33203125" customWidth="1"/>
+    <col min="4861" max="4861" width="19.44140625" customWidth="1"/>
+    <col min="4862" max="4862" width="2.88671875" customWidth="1"/>
+    <col min="4863" max="4863" width="5.5546875" customWidth="1"/>
+    <col min="4864" max="4864" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="4865" max="4865" width="23.33203125" customWidth="1"/>
+    <col min="4866" max="4866" width="10.33203125" customWidth="1"/>
+    <col min="4867" max="4867" width="19.44140625" customWidth="1"/>
+    <col min="4868" max="4868" width="9.33203125" customWidth="1"/>
+    <col min="4869" max="4870" width="19.44140625" customWidth="1"/>
+    <col min="5116" max="5116" width="7.33203125" customWidth="1"/>
+    <col min="5117" max="5117" width="19.44140625" customWidth="1"/>
+    <col min="5118" max="5118" width="2.88671875" customWidth="1"/>
+    <col min="5119" max="5119" width="5.5546875" customWidth="1"/>
+    <col min="5120" max="5120" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="5121" max="5121" width="23.33203125" customWidth="1"/>
+    <col min="5122" max="5122" width="10.33203125" customWidth="1"/>
+    <col min="5123" max="5123" width="19.44140625" customWidth="1"/>
+    <col min="5124" max="5124" width="9.33203125" customWidth="1"/>
+    <col min="5125" max="5126" width="19.44140625" customWidth="1"/>
+    <col min="5372" max="5372" width="7.33203125" customWidth="1"/>
+    <col min="5373" max="5373" width="19.44140625" customWidth="1"/>
+    <col min="5374" max="5374" width="2.88671875" customWidth="1"/>
+    <col min="5375" max="5375" width="5.5546875" customWidth="1"/>
+    <col min="5376" max="5376" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="5377" max="5377" width="23.33203125" customWidth="1"/>
+    <col min="5378" max="5378" width="10.33203125" customWidth="1"/>
+    <col min="5379" max="5379" width="19.44140625" customWidth="1"/>
+    <col min="5380" max="5380" width="9.33203125" customWidth="1"/>
+    <col min="5381" max="5382" width="19.44140625" customWidth="1"/>
+    <col min="5628" max="5628" width="7.33203125" customWidth="1"/>
+    <col min="5629" max="5629" width="19.44140625" customWidth="1"/>
+    <col min="5630" max="5630" width="2.88671875" customWidth="1"/>
+    <col min="5631" max="5631" width="5.5546875" customWidth="1"/>
+    <col min="5632" max="5632" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="5633" max="5633" width="23.33203125" customWidth="1"/>
+    <col min="5634" max="5634" width="10.33203125" customWidth="1"/>
+    <col min="5635" max="5635" width="19.44140625" customWidth="1"/>
+    <col min="5636" max="5636" width="9.33203125" customWidth="1"/>
+    <col min="5637" max="5638" width="19.44140625" customWidth="1"/>
+    <col min="5884" max="5884" width="7.33203125" customWidth="1"/>
+    <col min="5885" max="5885" width="19.44140625" customWidth="1"/>
+    <col min="5886" max="5886" width="2.88671875" customWidth="1"/>
+    <col min="5887" max="5887" width="5.5546875" customWidth="1"/>
+    <col min="5888" max="5888" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="5889" max="5889" width="23.33203125" customWidth="1"/>
+    <col min="5890" max="5890" width="10.33203125" customWidth="1"/>
+    <col min="5891" max="5891" width="19.44140625" customWidth="1"/>
+    <col min="5892" max="5892" width="9.33203125" customWidth="1"/>
+    <col min="5893" max="5894" width="19.44140625" customWidth="1"/>
+    <col min="6140" max="6140" width="7.33203125" customWidth="1"/>
+    <col min="6141" max="6141" width="19.44140625" customWidth="1"/>
+    <col min="6142" max="6142" width="2.88671875" customWidth="1"/>
+    <col min="6143" max="6143" width="5.5546875" customWidth="1"/>
+    <col min="6144" max="6144" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="6145" max="6145" width="23.33203125" customWidth="1"/>
+    <col min="6146" max="6146" width="10.33203125" customWidth="1"/>
+    <col min="6147" max="6147" width="19.44140625" customWidth="1"/>
+    <col min="6148" max="6148" width="9.33203125" customWidth="1"/>
+    <col min="6149" max="6150" width="19.44140625" customWidth="1"/>
+    <col min="6396" max="6396" width="7.33203125" customWidth="1"/>
+    <col min="6397" max="6397" width="19.44140625" customWidth="1"/>
+    <col min="6398" max="6398" width="2.88671875" customWidth="1"/>
+    <col min="6399" max="6399" width="5.5546875" customWidth="1"/>
+    <col min="6400" max="6400" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="6401" max="6401" width="23.33203125" customWidth="1"/>
+    <col min="6402" max="6402" width="10.33203125" customWidth="1"/>
+    <col min="6403" max="6403" width="19.44140625" customWidth="1"/>
+    <col min="6404" max="6404" width="9.33203125" customWidth="1"/>
+    <col min="6405" max="6406" width="19.44140625" customWidth="1"/>
+    <col min="6652" max="6652" width="7.33203125" customWidth="1"/>
+    <col min="6653" max="6653" width="19.44140625" customWidth="1"/>
+    <col min="6654" max="6654" width="2.88671875" customWidth="1"/>
+    <col min="6655" max="6655" width="5.5546875" customWidth="1"/>
+    <col min="6656" max="6656" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="6657" max="6657" width="23.33203125" customWidth="1"/>
+    <col min="6658" max="6658" width="10.33203125" customWidth="1"/>
+    <col min="6659" max="6659" width="19.44140625" customWidth="1"/>
+    <col min="6660" max="6660" width="9.33203125" customWidth="1"/>
+    <col min="6661" max="6662" width="19.44140625" customWidth="1"/>
+    <col min="6908" max="6908" width="7.33203125" customWidth="1"/>
+    <col min="6909" max="6909" width="19.44140625" customWidth="1"/>
+    <col min="6910" max="6910" width="2.88671875" customWidth="1"/>
+    <col min="6911" max="6911" width="5.5546875" customWidth="1"/>
+    <col min="6912" max="6912" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="6913" max="6913" width="23.33203125" customWidth="1"/>
+    <col min="6914" max="6914" width="10.33203125" customWidth="1"/>
+    <col min="6915" max="6915" width="19.44140625" customWidth="1"/>
+    <col min="6916" max="6916" width="9.33203125" customWidth="1"/>
+    <col min="6917" max="6918" width="19.44140625" customWidth="1"/>
+    <col min="7164" max="7164" width="7.33203125" customWidth="1"/>
+    <col min="7165" max="7165" width="19.44140625" customWidth="1"/>
+    <col min="7166" max="7166" width="2.88671875" customWidth="1"/>
+    <col min="7167" max="7167" width="5.5546875" customWidth="1"/>
+    <col min="7168" max="7168" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="7169" max="7169" width="23.33203125" customWidth="1"/>
+    <col min="7170" max="7170" width="10.33203125" customWidth="1"/>
+    <col min="7171" max="7171" width="19.44140625" customWidth="1"/>
+    <col min="7172" max="7172" width="9.33203125" customWidth="1"/>
+    <col min="7173" max="7174" width="19.44140625" customWidth="1"/>
+    <col min="7420" max="7420" width="7.33203125" customWidth="1"/>
+    <col min="7421" max="7421" width="19.44140625" customWidth="1"/>
+    <col min="7422" max="7422" width="2.88671875" customWidth="1"/>
+    <col min="7423" max="7423" width="5.5546875" customWidth="1"/>
+    <col min="7424" max="7424" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="7425" max="7425" width="23.33203125" customWidth="1"/>
+    <col min="7426" max="7426" width="10.33203125" customWidth="1"/>
+    <col min="7427" max="7427" width="19.44140625" customWidth="1"/>
+    <col min="7428" max="7428" width="9.33203125" customWidth="1"/>
+    <col min="7429" max="7430" width="19.44140625" customWidth="1"/>
+    <col min="7676" max="7676" width="7.33203125" customWidth="1"/>
+    <col min="7677" max="7677" width="19.44140625" customWidth="1"/>
+    <col min="7678" max="7678" width="2.88671875" customWidth="1"/>
+    <col min="7679" max="7679" width="5.5546875" customWidth="1"/>
+    <col min="7680" max="7680" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="7681" max="7681" width="23.33203125" customWidth="1"/>
+    <col min="7682" max="7682" width="10.33203125" customWidth="1"/>
+    <col min="7683" max="7683" width="19.44140625" customWidth="1"/>
+    <col min="7684" max="7684" width="9.33203125" customWidth="1"/>
+    <col min="7685" max="7686" width="19.44140625" customWidth="1"/>
+    <col min="7932" max="7932" width="7.33203125" customWidth="1"/>
+    <col min="7933" max="7933" width="19.44140625" customWidth="1"/>
+    <col min="7934" max="7934" width="2.88671875" customWidth="1"/>
+    <col min="7935" max="7935" width="5.5546875" customWidth="1"/>
+    <col min="7936" max="7936" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="7937" max="7937" width="23.33203125" customWidth="1"/>
+    <col min="7938" max="7938" width="10.33203125" customWidth="1"/>
+    <col min="7939" max="7939" width="19.44140625" customWidth="1"/>
+    <col min="7940" max="7940" width="9.33203125" customWidth="1"/>
+    <col min="7941" max="7942" width="19.44140625" customWidth="1"/>
+    <col min="8188" max="8188" width="7.33203125" customWidth="1"/>
+    <col min="8189" max="8189" width="19.44140625" customWidth="1"/>
+    <col min="8190" max="8190" width="2.88671875" customWidth="1"/>
+    <col min="8191" max="8191" width="5.5546875" customWidth="1"/>
+    <col min="8192" max="8192" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="8193" max="8193" width="23.33203125" customWidth="1"/>
+    <col min="8194" max="8194" width="10.33203125" customWidth="1"/>
+    <col min="8195" max="8195" width="19.44140625" customWidth="1"/>
+    <col min="8196" max="8196" width="9.33203125" customWidth="1"/>
+    <col min="8197" max="8198" width="19.44140625" customWidth="1"/>
+    <col min="8444" max="8444" width="7.33203125" customWidth="1"/>
+    <col min="8445" max="8445" width="19.44140625" customWidth="1"/>
+    <col min="8446" max="8446" width="2.88671875" customWidth="1"/>
+    <col min="8447" max="8447" width="5.5546875" customWidth="1"/>
+    <col min="8448" max="8448" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="8449" max="8449" width="23.33203125" customWidth="1"/>
+    <col min="8450" max="8450" width="10.33203125" customWidth="1"/>
+    <col min="8451" max="8451" width="19.44140625" customWidth="1"/>
+    <col min="8452" max="8452" width="9.33203125" customWidth="1"/>
+    <col min="8453" max="8454" width="19.44140625" customWidth="1"/>
+    <col min="8700" max="8700" width="7.33203125" customWidth="1"/>
+    <col min="8701" max="8701" width="19.44140625" customWidth="1"/>
+    <col min="8702" max="8702" width="2.88671875" customWidth="1"/>
+    <col min="8703" max="8703" width="5.5546875" customWidth="1"/>
+    <col min="8704" max="8704" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="8705" max="8705" width="23.33203125" customWidth="1"/>
+    <col min="8706" max="8706" width="10.33203125" customWidth="1"/>
+    <col min="8707" max="8707" width="19.44140625" customWidth="1"/>
+    <col min="8708" max="8708" width="9.33203125" customWidth="1"/>
+    <col min="8709" max="8710" width="19.44140625" customWidth="1"/>
+    <col min="8956" max="8956" width="7.33203125" customWidth="1"/>
+    <col min="8957" max="8957" width="19.44140625" customWidth="1"/>
+    <col min="8958" max="8958" width="2.88671875" customWidth="1"/>
+    <col min="8959" max="8959" width="5.5546875" customWidth="1"/>
+    <col min="8960" max="8960" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="8961" max="8961" width="23.33203125" customWidth="1"/>
+    <col min="8962" max="8962" width="10.33203125" customWidth="1"/>
+    <col min="8963" max="8963" width="19.44140625" customWidth="1"/>
+    <col min="8964" max="8964" width="9.33203125" customWidth="1"/>
+    <col min="8965" max="8966" width="19.44140625" customWidth="1"/>
+    <col min="9212" max="9212" width="7.33203125" customWidth="1"/>
+    <col min="9213" max="9213" width="19.44140625" customWidth="1"/>
+    <col min="9214" max="9214" width="2.88671875" customWidth="1"/>
+    <col min="9215" max="9215" width="5.5546875" customWidth="1"/>
+    <col min="9216" max="9216" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="9217" max="9217" width="23.33203125" customWidth="1"/>
+    <col min="9218" max="9218" width="10.33203125" customWidth="1"/>
+    <col min="9219" max="9219" width="19.44140625" customWidth="1"/>
+    <col min="9220" max="9220" width="9.33203125" customWidth="1"/>
+    <col min="9221" max="9222" width="19.44140625" customWidth="1"/>
+    <col min="9468" max="9468" width="7.33203125" customWidth="1"/>
+    <col min="9469" max="9469" width="19.44140625" customWidth="1"/>
+    <col min="9470" max="9470" width="2.88671875" customWidth="1"/>
+    <col min="9471" max="9471" width="5.5546875" customWidth="1"/>
+    <col min="9472" max="9472" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="9473" max="9473" width="23.33203125" customWidth="1"/>
+    <col min="9474" max="9474" width="10.33203125" customWidth="1"/>
+    <col min="9475" max="9475" width="19.44140625" customWidth="1"/>
+    <col min="9476" max="9476" width="9.33203125" customWidth="1"/>
+    <col min="9477" max="9478" width="19.44140625" customWidth="1"/>
+    <col min="9724" max="9724" width="7.33203125" customWidth="1"/>
+    <col min="9725" max="9725" width="19.44140625" customWidth="1"/>
+    <col min="9726" max="9726" width="2.88671875" customWidth="1"/>
+    <col min="9727" max="9727" width="5.5546875" customWidth="1"/>
+    <col min="9728" max="9728" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="9729" max="9729" width="23.33203125" customWidth="1"/>
+    <col min="9730" max="9730" width="10.33203125" customWidth="1"/>
+    <col min="9731" max="9731" width="19.44140625" customWidth="1"/>
+    <col min="9732" max="9732" width="9.33203125" customWidth="1"/>
+    <col min="9733" max="9734" width="19.44140625" customWidth="1"/>
+    <col min="9980" max="9980" width="7.33203125" customWidth="1"/>
+    <col min="9981" max="9981" width="19.44140625" customWidth="1"/>
+    <col min="9982" max="9982" width="2.88671875" customWidth="1"/>
+    <col min="9983" max="9983" width="5.5546875" customWidth="1"/>
+    <col min="9984" max="9984" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="9985" max="9985" width="23.33203125" customWidth="1"/>
+    <col min="9986" max="9986" width="10.33203125" customWidth="1"/>
+    <col min="9987" max="9987" width="19.44140625" customWidth="1"/>
+    <col min="9988" max="9988" width="9.33203125" customWidth="1"/>
+    <col min="9989" max="9990" width="19.44140625" customWidth="1"/>
+    <col min="10236" max="10236" width="7.33203125" customWidth="1"/>
+    <col min="10237" max="10237" width="19.44140625" customWidth="1"/>
+    <col min="10238" max="10238" width="2.88671875" customWidth="1"/>
+    <col min="10239" max="10239" width="5.5546875" customWidth="1"/>
+    <col min="10240" max="10240" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="10241" max="10241" width="23.33203125" customWidth="1"/>
+    <col min="10242" max="10242" width="10.33203125" customWidth="1"/>
+    <col min="10243" max="10243" width="19.44140625" customWidth="1"/>
+    <col min="10244" max="10244" width="9.33203125" customWidth="1"/>
+    <col min="10245" max="10246" width="19.44140625" customWidth="1"/>
+    <col min="10492" max="10492" width="7.33203125" customWidth="1"/>
+    <col min="10493" max="10493" width="19.44140625" customWidth="1"/>
+    <col min="10494" max="10494" width="2.88671875" customWidth="1"/>
+    <col min="10495" max="10495" width="5.5546875" customWidth="1"/>
+    <col min="10496" max="10496" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="10497" max="10497" width="23.33203125" customWidth="1"/>
+    <col min="10498" max="10498" width="10.33203125" customWidth="1"/>
+    <col min="10499" max="10499" width="19.44140625" customWidth="1"/>
+    <col min="10500" max="10500" width="9.33203125" customWidth="1"/>
+    <col min="10501" max="10502" width="19.44140625" customWidth="1"/>
+    <col min="10748" max="10748" width="7.33203125" customWidth="1"/>
+    <col min="10749" max="10749" width="19.44140625" customWidth="1"/>
+    <col min="10750" max="10750" width="2.88671875" customWidth="1"/>
+    <col min="10751" max="10751" width="5.5546875" customWidth="1"/>
+    <col min="10752" max="10752" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="10753" max="10753" width="23.33203125" customWidth="1"/>
+    <col min="10754" max="10754" width="10.33203125" customWidth="1"/>
+    <col min="10755" max="10755" width="19.44140625" customWidth="1"/>
+    <col min="10756" max="10756" width="9.33203125" customWidth="1"/>
+    <col min="10757" max="10758" width="19.44140625" customWidth="1"/>
+    <col min="11004" max="11004" width="7.33203125" customWidth="1"/>
+    <col min="11005" max="11005" width="19.44140625" customWidth="1"/>
+    <col min="11006" max="11006" width="2.88671875" customWidth="1"/>
+    <col min="11007" max="11007" width="5.5546875" customWidth="1"/>
+    <col min="11008" max="11008" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="11009" max="11009" width="23.33203125" customWidth="1"/>
+    <col min="11010" max="11010" width="10.33203125" customWidth="1"/>
+    <col min="11011" max="11011" width="19.44140625" customWidth="1"/>
+    <col min="11012" max="11012" width="9.33203125" customWidth="1"/>
+    <col min="11013" max="11014" width="19.44140625" customWidth="1"/>
+    <col min="11260" max="11260" width="7.33203125" customWidth="1"/>
+    <col min="11261" max="11261" width="19.44140625" customWidth="1"/>
+    <col min="11262" max="11262" width="2.88671875" customWidth="1"/>
+    <col min="11263" max="11263" width="5.5546875" customWidth="1"/>
+    <col min="11264" max="11264" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="11265" max="11265" width="23.33203125" customWidth="1"/>
+    <col min="11266" max="11266" width="10.33203125" customWidth="1"/>
+    <col min="11267" max="11267" width="19.44140625" customWidth="1"/>
+    <col min="11268" max="11268" width="9.33203125" customWidth="1"/>
+    <col min="11269" max="11270" width="19.44140625" customWidth="1"/>
+    <col min="11516" max="11516" width="7.33203125" customWidth="1"/>
+    <col min="11517" max="11517" width="19.44140625" customWidth="1"/>
+    <col min="11518" max="11518" width="2.88671875" customWidth="1"/>
+    <col min="11519" max="11519" width="5.5546875" customWidth="1"/>
+    <col min="11520" max="11520" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="11521" max="11521" width="23.33203125" customWidth="1"/>
+    <col min="11522" max="11522" width="10.33203125" customWidth="1"/>
+    <col min="11523" max="11523" width="19.44140625" customWidth="1"/>
+    <col min="11524" max="11524" width="9.33203125" customWidth="1"/>
+    <col min="11525" max="11526" width="19.44140625" customWidth="1"/>
+    <col min="11772" max="11772" width="7.33203125" customWidth="1"/>
+    <col min="11773" max="11773" width="19.44140625" customWidth="1"/>
+    <col min="11774" max="11774" width="2.88671875" customWidth="1"/>
+    <col min="11775" max="11775" width="5.5546875" customWidth="1"/>
+    <col min="11776" max="11776" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="11777" max="11777" width="23.33203125" customWidth="1"/>
+    <col min="11778" max="11778" width="10.33203125" customWidth="1"/>
+    <col min="11779" max="11779" width="19.44140625" customWidth="1"/>
+    <col min="11780" max="11780" width="9.33203125" customWidth="1"/>
+    <col min="11781" max="11782" width="19.44140625" customWidth="1"/>
+    <col min="12028" max="12028" width="7.33203125" customWidth="1"/>
+    <col min="12029" max="12029" width="19.44140625" customWidth="1"/>
+    <col min="12030" max="12030" width="2.88671875" customWidth="1"/>
+    <col min="12031" max="12031" width="5.5546875" customWidth="1"/>
+    <col min="12032" max="12032" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="12033" max="12033" width="23.33203125" customWidth="1"/>
+    <col min="12034" max="12034" width="10.33203125" customWidth="1"/>
+    <col min="12035" max="12035" width="19.44140625" customWidth="1"/>
+    <col min="12036" max="12036" width="9.33203125" customWidth="1"/>
+    <col min="12037" max="12038" width="19.44140625" customWidth="1"/>
+    <col min="12284" max="12284" width="7.33203125" customWidth="1"/>
+    <col min="12285" max="12285" width="19.44140625" customWidth="1"/>
+    <col min="12286" max="12286" width="2.88671875" customWidth="1"/>
+    <col min="12287" max="12287" width="5.5546875" customWidth="1"/>
+    <col min="12288" max="12288" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="12289" max="12289" width="23.33203125" customWidth="1"/>
+    <col min="12290" max="12290" width="10.33203125" customWidth="1"/>
+    <col min="12291" max="12291" width="19.44140625" customWidth="1"/>
+    <col min="12292" max="12292" width="9.33203125" customWidth="1"/>
+    <col min="12293" max="12294" width="19.44140625" customWidth="1"/>
+    <col min="12540" max="12540" width="7.33203125" customWidth="1"/>
+    <col min="12541" max="12541" width="19.44140625" customWidth="1"/>
+    <col min="12542" max="12542" width="2.88671875" customWidth="1"/>
+    <col min="12543" max="12543" width="5.5546875" customWidth="1"/>
+    <col min="12544" max="12544" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="12545" max="12545" width="23.33203125" customWidth="1"/>
+    <col min="12546" max="12546" width="10.33203125" customWidth="1"/>
+    <col min="12547" max="12547" width="19.44140625" customWidth="1"/>
+    <col min="12548" max="12548" width="9.33203125" customWidth="1"/>
+    <col min="12549" max="12550" width="19.44140625" customWidth="1"/>
+    <col min="12796" max="12796" width="7.33203125" customWidth="1"/>
+    <col min="12797" max="12797" width="19.44140625" customWidth="1"/>
+    <col min="12798" max="12798" width="2.88671875" customWidth="1"/>
+    <col min="12799" max="12799" width="5.5546875" customWidth="1"/>
+    <col min="12800" max="12800" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="12801" max="12801" width="23.33203125" customWidth="1"/>
+    <col min="12802" max="12802" width="10.33203125" customWidth="1"/>
+    <col min="12803" max="12803" width="19.44140625" customWidth="1"/>
+    <col min="12804" max="12804" width="9.33203125" customWidth="1"/>
+    <col min="12805" max="12806" width="19.44140625" customWidth="1"/>
+    <col min="13052" max="13052" width="7.33203125" customWidth="1"/>
+    <col min="13053" max="13053" width="19.44140625" customWidth="1"/>
+    <col min="13054" max="13054" width="2.88671875" customWidth="1"/>
+    <col min="13055" max="13055" width="5.5546875" customWidth="1"/>
+    <col min="13056" max="13056" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="13057" max="13057" width="23.33203125" customWidth="1"/>
+    <col min="13058" max="13058" width="10.33203125" customWidth="1"/>
+    <col min="13059" max="13059" width="19.44140625" customWidth="1"/>
+    <col min="13060" max="13060" width="9.33203125" customWidth="1"/>
+    <col min="13061" max="13062" width="19.44140625" customWidth="1"/>
+    <col min="13308" max="13308" width="7.33203125" customWidth="1"/>
+    <col min="13309" max="13309" width="19.44140625" customWidth="1"/>
+    <col min="13310" max="13310" width="2.88671875" customWidth="1"/>
+    <col min="13311" max="13311" width="5.5546875" customWidth="1"/>
+    <col min="13312" max="13312" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="13313" max="13313" width="23.33203125" customWidth="1"/>
+    <col min="13314" max="13314" width="10.33203125" customWidth="1"/>
+    <col min="13315" max="13315" width="19.44140625" customWidth="1"/>
+    <col min="13316" max="13316" width="9.33203125" customWidth="1"/>
+    <col min="13317" max="13318" width="19.44140625" customWidth="1"/>
+    <col min="13564" max="13564" width="7.33203125" customWidth="1"/>
+    <col min="13565" max="13565" width="19.44140625" customWidth="1"/>
+    <col min="13566" max="13566" width="2.88671875" customWidth="1"/>
+    <col min="13567" max="13567" width="5.5546875" customWidth="1"/>
+    <col min="13568" max="13568" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="13569" max="13569" width="23.33203125" customWidth="1"/>
+    <col min="13570" max="13570" width="10.33203125" customWidth="1"/>
+    <col min="13571" max="13571" width="19.44140625" customWidth="1"/>
+    <col min="13572" max="13572" width="9.33203125" customWidth="1"/>
+    <col min="13573" max="13574" width="19.44140625" customWidth="1"/>
+    <col min="13820" max="13820" width="7.33203125" customWidth="1"/>
+    <col min="13821" max="13821" width="19.44140625" customWidth="1"/>
+    <col min="13822" max="13822" width="2.88671875" customWidth="1"/>
+    <col min="13823" max="13823" width="5.5546875" customWidth="1"/>
+    <col min="13824" max="13824" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="13825" max="13825" width="23.33203125" customWidth="1"/>
+    <col min="13826" max="13826" width="10.33203125" customWidth="1"/>
+    <col min="13827" max="13827" width="19.44140625" customWidth="1"/>
+    <col min="13828" max="13828" width="9.33203125" customWidth="1"/>
+    <col min="13829" max="13830" width="19.44140625" customWidth="1"/>
+    <col min="14076" max="14076" width="7.33203125" customWidth="1"/>
+    <col min="14077" max="14077" width="19.44140625" customWidth="1"/>
+    <col min="14078" max="14078" width="2.88671875" customWidth="1"/>
+    <col min="14079" max="14079" width="5.5546875" customWidth="1"/>
+    <col min="14080" max="14080" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="14081" max="14081" width="23.33203125" customWidth="1"/>
+    <col min="14082" max="14082" width="10.33203125" customWidth="1"/>
+    <col min="14083" max="14083" width="19.44140625" customWidth="1"/>
+    <col min="14084" max="14084" width="9.33203125" customWidth="1"/>
+    <col min="14085" max="14086" width="19.44140625" customWidth="1"/>
+    <col min="14332" max="14332" width="7.33203125" customWidth="1"/>
+    <col min="14333" max="14333" width="19.44140625" customWidth="1"/>
+    <col min="14334" max="14334" width="2.88671875" customWidth="1"/>
+    <col min="14335" max="14335" width="5.5546875" customWidth="1"/>
+    <col min="14336" max="14336" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="14337" max="14337" width="23.33203125" customWidth="1"/>
+    <col min="14338" max="14338" width="10.33203125" customWidth="1"/>
+    <col min="14339" max="14339" width="19.44140625" customWidth="1"/>
+    <col min="14340" max="14340" width="9.33203125" customWidth="1"/>
+    <col min="14341" max="14342" width="19.44140625" customWidth="1"/>
+    <col min="14588" max="14588" width="7.33203125" customWidth="1"/>
+    <col min="14589" max="14589" width="19.44140625" customWidth="1"/>
+    <col min="14590" max="14590" width="2.88671875" customWidth="1"/>
+    <col min="14591" max="14591" width="5.5546875" customWidth="1"/>
+    <col min="14592" max="14592" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="14593" max="14593" width="23.33203125" customWidth="1"/>
+    <col min="14594" max="14594" width="10.33203125" customWidth="1"/>
+    <col min="14595" max="14595" width="19.44140625" customWidth="1"/>
+    <col min="14596" max="14596" width="9.33203125" customWidth="1"/>
+    <col min="14597" max="14598" width="19.44140625" customWidth="1"/>
+    <col min="14844" max="14844" width="7.33203125" customWidth="1"/>
+    <col min="14845" max="14845" width="19.44140625" customWidth="1"/>
+    <col min="14846" max="14846" width="2.88671875" customWidth="1"/>
+    <col min="14847" max="14847" width="5.5546875" customWidth="1"/>
+    <col min="14848" max="14848" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="14849" max="14849" width="23.33203125" customWidth="1"/>
+    <col min="14850" max="14850" width="10.33203125" customWidth="1"/>
+    <col min="14851" max="14851" width="19.44140625" customWidth="1"/>
+    <col min="14852" max="14852" width="9.33203125" customWidth="1"/>
+    <col min="14853" max="14854" width="19.44140625" customWidth="1"/>
+    <col min="15100" max="15100" width="7.33203125" customWidth="1"/>
+    <col min="15101" max="15101" width="19.44140625" customWidth="1"/>
+    <col min="15102" max="15102" width="2.88671875" customWidth="1"/>
+    <col min="15103" max="15103" width="5.5546875" customWidth="1"/>
+    <col min="15104" max="15104" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="15105" max="15105" width="23.33203125" customWidth="1"/>
+    <col min="15106" max="15106" width="10.33203125" customWidth="1"/>
+    <col min="15107" max="15107" width="19.44140625" customWidth="1"/>
+    <col min="15108" max="15108" width="9.33203125" customWidth="1"/>
+    <col min="15109" max="15110" width="19.44140625" customWidth="1"/>
+    <col min="15356" max="15356" width="7.33203125" customWidth="1"/>
+    <col min="15357" max="15357" width="19.44140625" customWidth="1"/>
+    <col min="15358" max="15358" width="2.88671875" customWidth="1"/>
+    <col min="15359" max="15359" width="5.5546875" customWidth="1"/>
+    <col min="15360" max="15360" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="15361" max="15361" width="23.33203125" customWidth="1"/>
+    <col min="15362" max="15362" width="10.33203125" customWidth="1"/>
+    <col min="15363" max="15363" width="19.44140625" customWidth="1"/>
+    <col min="15364" max="15364" width="9.33203125" customWidth="1"/>
+    <col min="15365" max="15366" width="19.44140625" customWidth="1"/>
+    <col min="15612" max="15612" width="7.33203125" customWidth="1"/>
+    <col min="15613" max="15613" width="19.44140625" customWidth="1"/>
+    <col min="15614" max="15614" width="2.88671875" customWidth="1"/>
+    <col min="15615" max="15615" width="5.5546875" customWidth="1"/>
+    <col min="15616" max="15616" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="15617" max="15617" width="23.33203125" customWidth="1"/>
+    <col min="15618" max="15618" width="10.33203125" customWidth="1"/>
+    <col min="15619" max="15619" width="19.44140625" customWidth="1"/>
+    <col min="15620" max="15620" width="9.33203125" customWidth="1"/>
+    <col min="15621" max="15622" width="19.44140625" customWidth="1"/>
+    <col min="15868" max="15868" width="7.33203125" customWidth="1"/>
+    <col min="15869" max="15869" width="19.44140625" customWidth="1"/>
+    <col min="15870" max="15870" width="2.88671875" customWidth="1"/>
+    <col min="15871" max="15871" width="5.5546875" customWidth="1"/>
+    <col min="15872" max="15872" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="15873" max="15873" width="23.33203125" customWidth="1"/>
+    <col min="15874" max="15874" width="10.33203125" customWidth="1"/>
+    <col min="15875" max="15875" width="19.44140625" customWidth="1"/>
+    <col min="15876" max="15876" width="9.33203125" customWidth="1"/>
+    <col min="15877" max="15878" width="19.44140625" customWidth="1"/>
+    <col min="16124" max="16124" width="7.33203125" customWidth="1"/>
+    <col min="16125" max="16125" width="19.44140625" customWidth="1"/>
+    <col min="16126" max="16126" width="2.88671875" customWidth="1"/>
+    <col min="16127" max="16127" width="5.5546875" customWidth="1"/>
+    <col min="16128" max="16128" width="90.33203125" bestFit="1" customWidth="1"/>
+    <col min="16129" max="16129" width="23.33203125" customWidth="1"/>
+    <col min="16130" max="16130" width="10.33203125" customWidth="1"/>
+    <col min="16131" max="16131" width="19.44140625" customWidth="1"/>
+    <col min="16132" max="16132" width="9.33203125" customWidth="1"/>
+    <col min="16133" max="16134" width="19.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>262</v>
       </c>
@@ -2710,7 +2719,7 @@
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
     </row>
-    <row r="2" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>433</v>
       </c>
@@ -2724,7 +2733,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>435</v>
       </c>
@@ -2738,7 +2747,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>436</v>
       </c>
@@ -2752,7 +2761,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>437</v>
       </c>
@@ -2766,7 +2775,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>438</v>
       </c>
@@ -2780,7 +2789,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>439</v>
       </c>
@@ -2794,7 +2803,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>440</v>
       </c>
@@ -2808,7 +2817,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>441</v>
       </c>
@@ -2822,7 +2831,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
@@ -2836,7 +2845,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
@@ -2850,7 +2859,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>6</v>
       </c>
@@ -2870,7 +2879,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>4</v>
       </c>
@@ -2884,7 +2893,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
@@ -2898,7 +2907,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>34</v>
       </c>
@@ -2918,7 +2927,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>10</v>
       </c>
@@ -2938,7 +2947,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -2958,7 +2967,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>13</v>
       </c>
@@ -2978,7 +2987,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>31</v>
       </c>
@@ -2998,7 +3007,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -3018,7 +3027,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>22</v>
       </c>
@@ -3038,7 +3047,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
@@ -3058,7 +3067,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>28</v>
       </c>
@@ -3078,7 +3087,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>37</v>
       </c>
@@ -3098,7 +3107,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>40</v>
       </c>
@@ -3118,7 +3127,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>43</v>
       </c>
@@ -3138,7 +3147,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -3158,7 +3167,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>49</v>
       </c>
@@ -3178,7 +3187,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>52</v>
       </c>
@@ -3198,7 +3207,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>55</v>
       </c>
@@ -3218,7 +3227,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>58</v>
       </c>
@@ -3238,7 +3247,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>61</v>
       </c>
@@ -3258,7 +3267,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>64</v>
       </c>
@@ -3278,7 +3287,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>67</v>
       </c>
@@ -3292,7 +3301,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>72</v>
       </c>
@@ -3312,7 +3321,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>75</v>
       </c>
@@ -3332,7 +3341,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>79</v>
       </c>
@@ -3352,7 +3361,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>69</v>
       </c>
@@ -3372,7 +3381,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>268</v>
       </c>
@@ -3386,7 +3395,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>82</v>
       </c>
@@ -3406,7 +3415,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>269</v>
       </c>
@@ -3426,7 +3435,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>85</v>
       </c>
@@ -3446,7 +3455,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>88</v>
       </c>
@@ -3466,7 +3475,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>91</v>
       </c>
@@ -3480,7 +3489,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>92</v>
       </c>
@@ -3494,7 +3503,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>93</v>
       </c>
@@ -3508,7 +3517,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>94</v>
       </c>
@@ -3522,7 +3531,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>95</v>
       </c>
@@ -3536,7 +3545,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>96</v>
       </c>
@@ -3550,7 +3559,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>97</v>
       </c>
@@ -3570,7 +3579,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>100</v>
       </c>
@@ -3590,7 +3599,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>103</v>
       </c>
@@ -3610,7 +3619,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>106</v>
       </c>
@@ -3630,7 +3639,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>109</v>
       </c>
@@ -3650,7 +3659,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>112</v>
       </c>
@@ -3670,7 +3679,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>113</v>
       </c>
@@ -3690,7 +3699,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>116</v>
       </c>
@@ -3710,7 +3719,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>117</v>
       </c>
@@ -3730,7 +3739,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>120</v>
       </c>
@@ -3750,7 +3759,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>123</v>
       </c>
@@ -3770,7 +3779,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>126</v>
       </c>
@@ -3790,7 +3799,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>129</v>
       </c>
@@ -3810,7 +3819,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>132</v>
       </c>
@@ -3830,7 +3839,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>135</v>
       </c>
@@ -3850,7 +3859,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>138</v>
       </c>
@@ -3870,7 +3879,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>141</v>
       </c>
@@ -3890,7 +3899,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>144</v>
       </c>
@@ -3910,7 +3919,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>147</v>
       </c>
@@ -3930,7 +3939,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>150</v>
       </c>
@@ -3950,7 +3959,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>379</v>
       </c>
@@ -3970,7 +3979,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>155</v>
       </c>
@@ -3990,7 +3999,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>158</v>
       </c>
@@ -4010,7 +4019,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>161</v>
       </c>
@@ -4030,7 +4039,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>164</v>
       </c>
@@ -4050,7 +4059,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>167</v>
       </c>
@@ -4070,7 +4079,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>170</v>
       </c>
@@ -4090,7 +4099,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>172</v>
       </c>
@@ -4110,7 +4119,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>174</v>
       </c>
@@ -4130,7 +4139,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>177</v>
       </c>
@@ -4150,7 +4159,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>180</v>
       </c>
@@ -4170,7 +4179,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>183</v>
       </c>
@@ -4190,7 +4199,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>207</v>
       </c>
@@ -4204,7 +4213,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>187</v>
       </c>
@@ -4224,7 +4233,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>190</v>
       </c>
@@ -4244,7 +4253,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>193</v>
       </c>
@@ -4258,7 +4267,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>195</v>
       </c>
@@ -4272,7 +4281,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>197</v>
       </c>
@@ -4292,7 +4301,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>200</v>
       </c>
@@ -4306,7 +4315,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>202</v>
       </c>
@@ -4320,7 +4329,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>204</v>
       </c>
@@ -4340,7 +4349,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>528</v>
       </c>
@@ -4357,7 +4366,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>208</v>
       </c>
@@ -4377,7 +4386,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>211</v>
       </c>
@@ -4397,7 +4406,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>214</v>
       </c>
@@ -4411,7 +4420,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>216</v>
       </c>
@@ -4425,7 +4434,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>218</v>
       </c>
@@ -4439,7 +4448,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>220</v>
       </c>
@@ -4453,7 +4462,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>222</v>
       </c>
@@ -4467,7 +4476,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>224</v>
       </c>
@@ -4481,7 +4490,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>226</v>
       </c>
@@ -4495,7 +4504,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>534</v>
       </c>
@@ -4509,7 +4518,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>228</v>
       </c>
@@ -4523,7 +4532,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>230</v>
       </c>
@@ -4537,7 +4546,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>232</v>
       </c>
@@ -4551,7 +4560,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>234</v>
       </c>
@@ -4565,7 +4574,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>236</v>
       </c>
@@ -4579,7 +4588,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>238</v>
       </c>
@@ -4593,7 +4602,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>240</v>
       </c>
@@ -4607,7 +4616,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>242</v>
       </c>
@@ -4621,7 +4630,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>244</v>
       </c>
@@ -4635,7 +4644,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>246</v>
       </c>
@@ -4649,7 +4658,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>364</v>
       </c>
@@ -4663,7 +4672,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>250</v>
       </c>
@@ -4677,7 +4686,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>252</v>
       </c>
@@ -4691,7 +4700,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>254</v>
       </c>
@@ -4705,9 +4714,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>256</v>
+        <v>538</v>
       </c>
       <c r="B116" t="s">
         <v>257</v>
@@ -4719,7 +4728,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>258</v>
       </c>
@@ -4733,7 +4742,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>260</v>
       </c>
@@ -4747,7 +4756,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>485</v>
       </c>
@@ -4788,12 +4797,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C971AAF2-4466-4291-9B0C-220F4CD0DB34}">
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.28515625" customWidth="1"/>
+    <col min="1" max="1" width="32.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>335</v>
       </c>
@@ -4801,7 +4810,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>454</v>
       </c>
@@ -4809,7 +4818,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>530</v>
       </c>
@@ -4817,7 +4826,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>443</v>
       </c>
@@ -4825,7 +4834,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>450</v>
       </c>
@@ -4833,7 +4842,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>445</v>
       </c>
@@ -4841,7 +4850,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>418</v>
       </c>
@@ -4849,7 +4858,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>419</v>
       </c>
@@ -4857,7 +4866,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>532</v>
       </c>
@@ -4865,7 +4874,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>469</v>
       </c>
@@ -4873,7 +4882,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>420</v>
       </c>
@@ -4881,7 +4890,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>421</v>
       </c>
@@ -4889,7 +4898,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>422</v>
       </c>
@@ -4897,7 +4906,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>447</v>
       </c>
@@ -4905,7 +4914,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>449</v>
       </c>
@@ -4913,7 +4922,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>448</v>
       </c>
@@ -4921,7 +4930,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>453</v>
       </c>
@@ -4929,7 +4938,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>463</v>
       </c>
@@ -4949,13 +4958,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3D59AA9-70E3-4D83-9720-9F1B6570621A}">
   <dimension ref="A1:C184"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>262</v>
       </c>
@@ -4963,52 +4972,52 @@
         <v>354</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>100</v>
       </c>
@@ -5017,7 +5026,7 @@
       </c>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>129</v>
       </c>
@@ -5026,37 +5035,37 @@
       </c>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>230</v>
       </c>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>158</v>
       </c>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>211</v>
       </c>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>222</v>
       </c>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>232</v>
       </c>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>320</v>
       </c>
@@ -5064,17 +5073,17 @@
         <v>476</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -5083,24 +5092,24 @@
       </c>
       <c r="C21" s="1"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>208</v>
       </c>
       <c r="C23" s="1"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>254</v>
       </c>
       <c r="C24" s="1"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>314</v>
       </c>
@@ -5108,7 +5117,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>315</v>
       </c>
@@ -5116,7 +5125,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>248</v>
       </c>
@@ -5124,19 +5133,19 @@
         <v>365</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>364</v>
       </c>
       <c r="C28" s="1"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>260</v>
       </c>
       <c r="C29" s="1"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>172</v>
       </c>
@@ -5145,7 +5154,7 @@
       </c>
       <c r="C30" s="1"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>329</v>
       </c>
@@ -5153,19 +5162,19 @@
         <v>367</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>216</v>
       </c>
       <c r="C32" s="1"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>147</v>
       </c>
       <c r="C33" s="1"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>309</v>
       </c>
@@ -5173,18 +5182,18 @@
         <v>368</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>161</v>
       </c>
       <c r="C35" s="1"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>285</v>
       </c>
@@ -5192,12 +5201,12 @@
         <v>482</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>282</v>
       </c>
@@ -5205,7 +5214,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>19</v>
       </c>
@@ -5214,13 +5223,13 @@
       </c>
       <c r="C40" s="1"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>240</v>
       </c>
       <c r="C41" s="1"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>371</v>
       </c>
@@ -5228,7 +5237,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>268</v>
       </c>
@@ -5237,19 +5246,19 @@
       </c>
       <c r="C43" s="1"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>167</v>
       </c>
       <c r="C44" s="1"/>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>238</v>
       </c>
       <c r="C45" s="1"/>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>69</v>
       </c>
@@ -5258,17 +5267,17 @@
       </c>
       <c r="C46" s="1"/>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>293</v>
       </c>
@@ -5276,29 +5285,29 @@
         <v>525</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="1"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>214</v>
       </c>
       <c r="C52" s="1"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>226</v>
       </c>
@@ -5307,19 +5316,19 @@
       </c>
       <c r="C54" s="1"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>202</v>
       </c>
       <c r="C55" s="1"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>177</v>
       </c>
       <c r="C56" s="1"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>183</v>
       </c>
@@ -5328,13 +5337,13 @@
       </c>
       <c r="C57" s="1"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>135</v>
       </c>
       <c r="C58" s="1"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>288</v>
       </c>
@@ -5342,18 +5351,18 @@
         <v>527</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>180</v>
       </c>
       <c r="C60" s="1"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>275</v>
       </c>
@@ -5361,7 +5370,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>116</v>
       </c>
@@ -5370,23 +5379,23 @@
       </c>
       <c r="C63" s="1"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>256</v>
       </c>
       <c r="C66" s="1"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>37</v>
       </c>
@@ -5395,13 +5404,13 @@
       </c>
       <c r="C67" s="1"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>224</v>
       </c>
       <c r="C68" s="1"/>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>25</v>
       </c>
@@ -5410,7 +5419,7 @@
       </c>
       <c r="C69" s="1"/>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>79</v>
       </c>
@@ -5419,7 +5428,7 @@
       </c>
       <c r="C70" s="1"/>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>207</v>
       </c>
@@ -5428,13 +5437,13 @@
       </c>
       <c r="C71" s="1"/>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>528</v>
       </c>
       <c r="C72" s="1"/>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>220</v>
       </c>
@@ -5443,30 +5452,30 @@
       </c>
       <c r="C73" s="1"/>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>94</v>
       </c>
       <c r="C74" s="1"/>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C75" s="1"/>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C76" s="1"/>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>75</v>
       </c>
@@ -5475,7 +5484,7 @@
       </c>
       <c r="C78" s="1"/>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>279</v>
       </c>
@@ -5483,7 +5492,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>113</v>
       </c>
@@ -5492,7 +5501,7 @@
       </c>
       <c r="C80" s="1"/>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>534</v>
       </c>
@@ -5501,18 +5510,18 @@
       </c>
       <c r="C81" s="1"/>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>170</v>
       </c>
       <c r="C82" s="1"/>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>88</v>
       </c>
@@ -5521,19 +5530,19 @@
       </c>
       <c r="C84" s="1"/>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>379</v>
       </c>
       <c r="C85" s="1"/>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>244</v>
       </c>
       <c r="C86" s="1"/>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>174</v>
       </c>
@@ -5542,7 +5551,7 @@
       </c>
       <c r="C87" s="1"/>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>28</v>
       </c>
@@ -5551,7 +5560,7 @@
       </c>
       <c r="C88" s="1"/>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>82</v>
       </c>
@@ -5560,13 +5569,13 @@
       </c>
       <c r="C89" s="1"/>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C90" s="1"/>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>55</v>
       </c>
@@ -5575,7 +5584,7 @@
       </c>
       <c r="C91" s="1"/>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>195</v>
       </c>
@@ -5584,7 +5593,7 @@
       </c>
       <c r="C92" s="1"/>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>286</v>
       </c>
@@ -5592,23 +5601,23 @@
         <v>383</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>252</v>
       </c>
       <c r="C96" s="1"/>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>106</v>
       </c>
@@ -5617,31 +5626,31 @@
       </c>
       <c r="C97" s="1"/>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C98" s="1"/>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>197</v>
       </c>
       <c r="C99" s="1"/>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>200</v>
       </c>
       <c r="C100" s="1"/>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C101" s="1"/>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>103</v>
       </c>
@@ -5650,13 +5659,13 @@
       </c>
       <c r="C102" s="1"/>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>132</v>
       </c>
       <c r="C103" s="1"/>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>319</v>
       </c>
@@ -5664,13 +5673,13 @@
         <v>472</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>164</v>
       </c>
       <c r="C105" s="1"/>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>193</v>
       </c>
@@ -5679,7 +5688,7 @@
       </c>
       <c r="C106" s="1"/>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>323</v>
       </c>
@@ -5687,7 +5696,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>126</v>
       </c>
@@ -5696,19 +5705,19 @@
       </c>
       <c r="C108" s="1"/>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C109" s="1"/>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>242</v>
       </c>
       <c r="C110" s="1"/>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>273</v>
       </c>
@@ -5716,7 +5725,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>292</v>
       </c>
@@ -5724,17 +5733,17 @@
         <v>389</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>321</v>
       </c>
@@ -5742,12 +5751,12 @@
         <v>483</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>22</v>
       </c>
@@ -5756,7 +5765,7 @@
       </c>
       <c r="C117" s="1"/>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>85</v>
       </c>
@@ -5765,18 +5774,18 @@
       </c>
       <c r="C118" s="1"/>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>91</v>
       </c>
       <c r="C119" s="1"/>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>310</v>
       </c>
@@ -5784,30 +5793,30 @@
         <v>474</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>250</v>
       </c>
       <c r="C122" s="1"/>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>485</v>
       </c>
       <c r="C123" s="1"/>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>228</v>
       </c>
       <c r="C125" s="1"/>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>280</v>
       </c>
@@ -5815,7 +5824,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>97</v>
       </c>
@@ -5824,46 +5833,46 @@
       </c>
       <c r="C127" s="1"/>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>144</v>
       </c>
       <c r="C128" s="1"/>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>96</v>
       </c>
       <c r="C132" s="1"/>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>204</v>
       </c>
       <c r="C133" s="1"/>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>218</v>
       </c>
       <c r="C134" s="1"/>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>190</v>
       </c>
@@ -5872,24 +5881,24 @@
       </c>
       <c r="C135" s="1"/>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>123</v>
       </c>
       <c r="C136" s="1"/>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>246</v>
       </c>
       <c r="C138" s="1"/>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>326</v>
       </c>
@@ -5897,7 +5906,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>64</v>
       </c>
@@ -5906,57 +5915,57 @@
       </c>
       <c r="C140" s="1"/>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>93</v>
       </c>
       <c r="C141" s="1"/>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>155</v>
       </c>
       <c r="C142" s="1"/>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C144" s="1"/>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C148" s="1"/>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>138</v>
       </c>
       <c r="C149" s="1"/>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>187</v>
       </c>
@@ -5965,7 +5974,7 @@
       </c>
       <c r="C150" s="1"/>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>72</v>
       </c>
@@ -5974,7 +5983,7 @@
       </c>
       <c r="C151" s="1"/>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>317</v>
       </c>
@@ -5982,7 +5991,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>283</v>
       </c>
@@ -5990,7 +5999,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>61</v>
       </c>
@@ -5999,31 +6008,31 @@
       </c>
       <c r="C154" s="1"/>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>141</v>
       </c>
       <c r="C155" s="1"/>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C156" s="1"/>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>269</v>
       </c>
       <c r="C157" s="1"/>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>150</v>
       </c>
       <c r="C158" s="1"/>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>46</v>
       </c>
@@ -6032,12 +6041,12 @@
       </c>
       <c r="C159" s="1"/>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>67</v>
       </c>
@@ -6046,23 +6055,23 @@
       </c>
       <c r="C161" s="1"/>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>112</v>
       </c>
       <c r="C164" s="1"/>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>31</v>
       </c>
@@ -6071,7 +6080,7 @@
       </c>
       <c r="C165" s="1"/>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>49</v>
       </c>
@@ -6080,7 +6089,7 @@
       </c>
       <c r="C166" s="1"/>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>40</v>
       </c>
@@ -6089,28 +6098,28 @@
       </c>
       <c r="C167" s="1"/>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C169" s="1"/>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>294</v>
       </c>
@@ -6118,13 +6127,13 @@
         <v>442</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>258</v>
       </c>
       <c r="C173" s="1"/>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>117</v>
       </c>
@@ -6133,7 +6142,7 @@
       </c>
       <c r="C174" s="1"/>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>289</v>
       </c>
@@ -6141,7 +6150,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>281</v>
       </c>
@@ -6149,13 +6158,13 @@
         <v>484</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>234</v>
       </c>
       <c r="C177" s="1"/>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>52</v>
       </c>
@@ -6164,12 +6173,12 @@
       </c>
       <c r="C178" s="1"/>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>58</v>
       </c>
@@ -6178,7 +6187,7 @@
       </c>
       <c r="C180" s="1"/>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>120</v>
       </c>
@@ -6187,13 +6196,13 @@
       </c>
       <c r="C181" s="1"/>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>236</v>
       </c>
       <c r="C182" s="1"/>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>287</v>
       </c>
@@ -6201,7 +6210,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>109</v>
       </c>
@@ -6221,13 +6230,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F16A59D4-DD96-4271-9DA3-B66DD057B3BD}">
-  <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="27.5703125" customWidth="1"/>
+    <col min="2" max="2" width="27.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>262</v>
       </c>
@@ -6238,7 +6247,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -6249,7 +6258,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -6260,7 +6269,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>282</v>
       </c>
@@ -6271,7 +6280,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>187</v>
       </c>
@@ -6282,7 +6291,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>187</v>
       </c>
@@ -6293,7 +6302,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>187</v>
       </c>
@@ -6304,7 +6313,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>187</v>
       </c>
@@ -6315,7 +6324,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>172</v>
       </c>
@@ -6326,7 +6335,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>172</v>
       </c>
@@ -6337,7 +6346,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>172</v>
       </c>
@@ -6348,7 +6357,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>172</v>
       </c>
@@ -6359,7 +6368,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>67</v>
       </c>
@@ -6370,7 +6379,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>67</v>
       </c>
@@ -6381,7 +6390,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>61</v>
       </c>
@@ -6392,7 +6401,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>61</v>
       </c>
@@ -6403,7 +6412,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>289</v>
       </c>
@@ -6414,7 +6423,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>289</v>
       </c>
@@ -6425,7 +6434,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>126</v>
       </c>
@@ -6436,7 +6445,27 @@
         <v>466</v>
       </c>
     </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>174</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B20" r:id="rId1" xr:uid="{794CC3AE-5CEB-47E6-A3B3-D8943A8315A7}"/>
+    <hyperlink ref="B21" r:id="rId2" xr:uid="{A109154D-C9CD-4DFF-B156-C55B1CE805C1}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SUKCO0665\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB2C0C8-74D8-4257-B448-833025637023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342C99BF-CA6F-4EF9-AE1A-3FAEF5BC0A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" activeTab="3" xr2:uid="{4E7050FE-42BA-4739-8710-2FFE42CC73BF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="541">
   <si>
     <t>Sridhar Durve</t>
   </si>
@@ -6230,7 +6230,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F16A59D4-DD96-4271-9DA3-B66DD057B3BD}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27.5546875" customWidth="1"/>
@@ -6459,6 +6459,14 @@
       </c>
       <c r="B21" s="2" t="s">
         <v>540</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>315</v>
+      </c>
+      <c r="B22" t="s">
+        <v>423</v>
       </c>
     </row>
   </sheetData>
